--- a/Files/Risk_Assessment.xlsx
+++ b/Files/Risk_Assessment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Graham\Desktop\Uni\Grad Cert IT\Networking and Cyber Security\Group Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97577977-2FA7-4419-9937-96FA86164A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2794A8F3-DD8A-46A1-8895-7781B848A2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14460" yWindow="0" windowWidth="36930" windowHeight="20985" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26655" yWindow="900" windowWidth="24930" windowHeight="19485" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="10" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="InfoSecThreats" sheetId="1" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Vulnerabilities!$A$1:$L$444</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Vulnerabilities!$A$1:$L$443</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="112">
   <si>
     <t>ThreatNum</t>
   </si>
@@ -168,15 +168,6 @@
     <t>VulnNum</t>
   </si>
   <si>
-    <t>User accidentally transfer money to the wrong bank account</t>
-  </si>
-  <si>
-    <t>Key logger on home computer records bank login details</t>
-  </si>
-  <si>
-    <t>DoS attack on login prevents access to bank account</t>
-  </si>
-  <si>
     <t>Likelihood</t>
   </si>
   <si>
@@ -241,325 +232,163 @@
     <t>RiskValues</t>
   </si>
   <si>
-    <t>Employee data (HR records, payroll, personal information)</t>
-  </si>
-  <si>
-    <t>Financial data (accounting records, invoices, tax data)</t>
-  </si>
-  <si>
-    <t>Backup Data</t>
-  </si>
-  <si>
-    <t>Routers and firewalls</t>
-  </si>
-  <si>
-    <t>Printers and scanners</t>
-  </si>
-  <si>
-    <t>Uninterruptible Power Supplies (UPS)</t>
-  </si>
-  <si>
-    <t>Racks, cabling (Ethernet, fibre), patch panels</t>
-  </si>
-  <si>
-    <t>Operating systems (Windows Server, Linux, Windows/macOS clients)</t>
-  </si>
-  <si>
-    <t>Accounting and finance software</t>
-  </si>
-  <si>
-    <t>CRM software</t>
-  </si>
-  <si>
-    <t>Website and web applications</t>
-  </si>
-  <si>
-    <t>Network management and monitoring tools</t>
-  </si>
-  <si>
-    <t>Security software (antivirus, endpoint protection)</t>
-  </si>
-  <si>
-    <t>Internet connections (ISP)</t>
-  </si>
-  <si>
-    <t>Firewalls and security gateways</t>
-  </si>
-  <si>
-    <t>Network addressing</t>
-  </si>
-  <si>
-    <t>Network design and configuration processes</t>
-  </si>
-  <si>
-    <t>Access control and identity management processes</t>
-  </si>
-  <si>
-    <t>Data backup and disaster recovery procedures</t>
-  </si>
-  <si>
-    <t>IT service management and support workflows</t>
-  </si>
-  <si>
-    <t>Onboarding and offboarding procedures for staff</t>
-  </si>
-  <si>
-    <t>Physical security procedures (building and access control)</t>
-  </si>
-  <si>
-    <t>Risk management and business continuity planning</t>
-  </si>
-  <si>
-    <t>Bank Account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desktop computers and laptops </t>
-  </si>
-  <si>
-    <t>Malware installed via malicious software hidden inside pirated copy of software</t>
-  </si>
-  <si>
-    <t>Unable to use software impacting workflow</t>
-  </si>
-  <si>
-    <t>Incorrect entries, deletions</t>
-  </si>
-  <si>
-    <t>ransomware encryption of data impacting workflow</t>
-  </si>
-  <si>
-    <t>BEC using CRM info for use in scam</t>
-  </si>
-  <si>
-    <t>Ransomeware attack that encrypts and breach exposing contacts details</t>
-  </si>
-  <si>
-    <t>Backup storage failure resulting in lost data</t>
-  </si>
-  <si>
-    <t>Payroll file uploaded to a non-business account with no security or incorrect data entry</t>
-  </si>
-  <si>
-    <t>Data accessed through theft of device or unsecured access points</t>
-  </si>
-  <si>
-    <t>Threat actor steals HR records and threatens to share publicly</t>
-  </si>
-  <si>
-    <t>Loss of records due to natural disaster resulting in non-compliance</t>
-  </si>
-  <si>
-    <t>Ransomeware attack during BAS or EOFY period</t>
-  </si>
-  <si>
-    <t>Backup hardware failures without redundancy in system</t>
-  </si>
-  <si>
     <t>Credential theft leading to unauthorised payments</t>
-  </si>
-  <si>
-    <t>Failure to change default passwords or setting inadequate data retention periods.</t>
   </si>
   <si>
     <t>Missing MFA on remote access enables unauthorized viewing via password attacks.</t>
   </si>
   <si>
-    <t>Risk of physical theft or destruction due to unsecured location.</t>
-  </si>
-  <si>
-    <t>Laptop stolen and passwords are written in permanent marker on device</t>
-  </si>
-  <si>
-    <t>Inadequate physical security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff </t>
-  </si>
-  <si>
-    <t>Customer Data</t>
-  </si>
-  <si>
-    <t>CRM</t>
-  </si>
-  <si>
     <t>Switch</t>
   </si>
   <si>
-    <t>Wireless networks</t>
+    <t>PCs</t>
   </si>
   <si>
-    <t>Customers</t>
+    <t>Router</t>
   </si>
   <si>
-    <t>Onboarding and offboarding procedures for customers</t>
+    <t>OpenWRT</t>
   </si>
   <si>
-    <t>User accidentally deletes customer data</t>
+    <t>Server / VM Host</t>
   </si>
   <si>
-    <t>Someone breaks into bussiness and steals server PC with data</t>
+    <t>LuCI</t>
   </si>
   <si>
-    <t>Loss of data due to system damage from natural disaster</t>
+    <t>Accounting Software</t>
   </si>
   <si>
-    <t>Employee data accidentally deleted</t>
+    <t xml:space="preserve">Dropbear SSH </t>
   </si>
   <si>
-    <t>Disgruntled staff member provides data to competitor</t>
+    <t>Manager</t>
   </si>
   <si>
-    <t>Disgruntled staff take customer data with them to a competitor</t>
+    <t>Accountants</t>
   </si>
   <si>
-    <t>Unable to use hardware due to hacking</t>
+    <t>Bookkeeper</t>
   </si>
   <si>
-    <t>Short circuit of power due to natural event</t>
+    <t>IT Support worker</t>
   </si>
   <si>
-    <t>Risk of physical theft</t>
+    <t>LAN 88.1.1.0/24</t>
   </si>
   <si>
-    <t>Rick of damage from natural event such as storm</t>
+    <t>VM network 192.168.56.0/24</t>
   </si>
   <si>
-    <t>Hardware becomes outdated which results in failures</t>
+    <t>WAN Connection 10.0.3.15/24</t>
   </si>
   <si>
-    <t>Unauthorised access</t>
+    <t>Client Tax Records</t>
   </si>
   <si>
-    <t>An attacker exploits an unpatched website or application vulnerability</t>
+    <t>Payroll Data</t>
   </si>
   <si>
-    <t>An error causes the website to crash, display incorrect info or become unavailable</t>
+    <t>Financial Statements</t>
   </si>
   <si>
-    <t>An attacker exploits a CMR vulnerability</t>
+    <t>Website content</t>
   </si>
   <si>
-    <t>An employee accidentally locks access to the system</t>
+    <t>Firewall management</t>
   </si>
   <si>
-    <t>A software bug or failed update error makes the system unavailable</t>
+    <t>Access to the SSH server</t>
   </si>
   <si>
-    <t>Outdated security software cannot detect new threats</t>
+    <t>Backup procedure</t>
   </si>
   <si>
-    <t>The software failes to detect and block malware</t>
+    <t>Phishing emails lead to a malware infection</t>
   </si>
   <si>
-    <t>Incorrect configuration preveents access to the network</t>
+    <t>PCs that are vulnerable to malware</t>
   </si>
   <si>
-    <t>Unauthorised access to the network and alters or disables the configurations</t>
+    <t>Ransomware extracts sensitive client data</t>
   </si>
   <si>
-    <t>A fault or failed updated causes the monitoring tools to stop working</t>
+    <t>Firewall rules have been  misconfigured</t>
   </si>
   <si>
-    <t>The modem fails disrupting internet access</t>
+    <t xml:space="preserve">Attempt to access SSH </t>
   </si>
   <si>
-    <t>An ISP outage restricts internet access</t>
+    <t>Failure leads to LAN disconnection</t>
   </si>
   <si>
-    <t xml:space="preserve">Incorrect rules are created </t>
+    <t>Physical tampering with ports</t>
   </si>
   <si>
-    <t>An attack which exploits vulnerabilities and permits unauthorised access</t>
+    <t>Incorrect settings could expose network</t>
   </si>
   <si>
-    <t>The hardware fails and interupts connections</t>
+    <t>Outdated OpenWRT version could lead to vulnerabilities</t>
   </si>
   <si>
-    <t>Weak Wi-Fi passwords allows unauthorised access to the network</t>
+    <t>Dropbear bugs causes crashes</t>
   </si>
   <si>
-    <t>Employees are creating weak passwords</t>
+    <t>LuCI doesn't use the more secure HTTPS</t>
   </si>
   <si>
-    <t>Malware or softwre intercepts the network and creates fake access points</t>
+    <t>Malware could alter tax calculations</t>
   </si>
   <si>
-    <t>The wrong configurations prevent devices from communicating</t>
+    <t>Attackers could detect SSH on port 2222</t>
   </si>
   <si>
-    <t>DNS failures prevents devices from obtaining addresses</t>
+    <t>Manager could have too much admin access without the correct training</t>
   </si>
   <si>
-    <t>Management</t>
+    <t>Accidental leak of customer data</t>
   </si>
   <si>
-    <t xml:space="preserve">Management approved inadequate safety procedures </t>
+    <t>VM host could be compromised</t>
   </si>
   <si>
-    <t>Accessible accounts provides access to sensitive customer and financial data</t>
+    <t>Payroll and financial data mishandling</t>
   </si>
   <si>
-    <t>Employess disclose credentials from a phishing attack</t>
+    <t xml:space="preserve">Access has been misconfigured </t>
   </si>
   <si>
-    <t>Employees steals confidential business information</t>
+    <t>Internet outtage could stop work from being completed</t>
   </si>
   <si>
-    <t>Attackers use phishing and malware to access customer data</t>
+    <t xml:space="preserve">Attack on the VM network </t>
   </si>
   <si>
-    <t>Customer data is used to extort from the business</t>
+    <t>The incorrect connection settings could expose services to attacker</t>
   </si>
   <si>
-    <t>Incorrect configuration exposes the network to malware attacks</t>
+    <t>The data is a target for extortion</t>
   </si>
   <si>
-    <t>The network design becomes outdated</t>
+    <t>The payroll data is supplied to the wrong recipient</t>
   </si>
   <si>
-    <t>Excessive or incorrect permissions are granted to staff</t>
+    <t>Attackers could alter financial reports with malware</t>
   </si>
   <si>
-    <t>Weak MFA allows unauthorised access</t>
+    <t>Attackers could modify website pages</t>
   </si>
   <si>
-    <t>Backup software fails</t>
+    <t>Rules could be misconfigured which provides unauthorised access</t>
   </si>
   <si>
-    <t>Important data is missed from backups</t>
+    <t>Weak authentiction could give unauthorised persons access</t>
   </si>
   <si>
-    <t>Natural events cause damage to the systems and hardware that stores the data</t>
+    <t>Incomplete backups could cause loss of tax records</t>
   </si>
   <si>
-    <t>Incorrect customer data is entered</t>
-  </si>
-  <si>
-    <t>Weak security allows fake customer data to be created</t>
-  </si>
-  <si>
-    <t>Incorrect or irrelevant employee data is captured</t>
-  </si>
-  <si>
-    <t>Training for employees is not sufficient</t>
-  </si>
-  <si>
-    <t>Important risks are overlooked</t>
-  </si>
-  <si>
-    <t>Inadequate preparation causes extended disruption</t>
-  </si>
-  <si>
-    <t>Employees leaves restricted areas accessible to the public</t>
-  </si>
-  <si>
-    <t>Unauthorised access is given to an unauthorised person</t>
-  </si>
-  <si>
-    <t>An incorrect system change causes an outage</t>
-  </si>
-  <si>
-    <t>An attacker impersonates a staff member giving unauthorised access</t>
+    <t>Backups that aren't encrypted exposes data to theft</t>
   </si>
 </sst>
 </file>
@@ -1118,20 +947,20 @@
   <sheetData>
     <row r="1" spans="1:2" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="294" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="243" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1166,10 +995,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1177,10 +1006,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1188,10 +1017,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1199,10 +1028,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1210,10 +1039,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1221,10 +1050,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1232,10 +1061,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1243,10 +1072,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1254,10 +1083,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1265,10 +1094,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1276,10 +1105,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1287,10 +1116,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1298,10 +1127,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1309,10 +1138,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1320,10 +1149,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1331,10 +1160,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -1342,10 +1171,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E18" s="22"/>
     </row>
@@ -1354,10 +1183,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1365,10 +1194,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1376,10 +1205,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -1387,10 +1216,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E22" s="22"/>
     </row>
@@ -1399,207 +1228,135 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" t="s">
-        <v>145</v>
-      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" t="s">
-        <v>106</v>
-      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" t="s">
-        <v>111</v>
-      </c>
       <c r="E27" s="21"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" t="s">
-        <v>78</v>
-      </c>
     </row>
     <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" t="s">
-        <v>79</v>
-      </c>
       <c r="E29" s="22"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31" t="s">
-        <v>82</v>
-      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C33" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1889,15 +1646,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C2DAE8-51BF-4509-BC4F-A78D257FBFC8}">
-  <dimension ref="A1:N444"/>
+  <dimension ref="A1:N443"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" customWidth="1"/>
-    <col min="2" max="2" width="34.42578125" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="2" max="3" width="34.85546875" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="65.28515625" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" customWidth="1"/>
     <col min="8" max="8" width="74" customWidth="1"/>
     <col min="9" max="11" width="10.7109375" customWidth="1"/>
   </cols>
@@ -1928,16 +1684,16 @@
         <v>38</v>
       </c>
       <c r="I1" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" s="24" t="s">
         <v>43</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="K1" t="s">
-        <v>45</v>
-      </c>
-      <c r="L1" s="24" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -1953,11 +1709,11 @@
       </c>
       <c r="D2" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C2,Assets!A:C,2,FALSE),"")</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="E2" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C2,Assets!A:C,3,FALSE),"")</f>
-        <v>Bank Account</v>
+        <v>PCs</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1967,20 +1723,20 @@
         <v>T1V1A1</v>
       </c>
       <c r="H2" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K2" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I2,"|",J2),RiskValues!C:D,2,FALSE),"")</f>
         <v>Moderate</v>
       </c>
       <c r="L2">
-        <v>63</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -1996,666 +1752,668 @@
       </c>
       <c r="D3" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C3,Assets!A:C,2,FALSE),"")</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="E3" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C3,Assets!A:C,3,FALSE),"")</f>
-        <v>Bank Account</v>
+        <v>PCs</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="str">
-        <f t="shared" ref="G3:G109" si="0">IF(ISBLANK(F3),"",_xlfn.CONCAT("T",A3,"V",F3,"A",C3))</f>
-        <v>T2V1A1</v>
+        <f t="shared" ref="G3:G108" si="0">IF(ISBLANK(F3),"",_xlfn.CONCAT("T",A3,"V",F3,"A",C3))</f>
+        <v>T2V2A1</v>
       </c>
       <c r="H3" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="I3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K3" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I3,"|",J3),RiskValues!C:D,2,FALSE),"")</f>
-        <v>High</v>
+        <v>Moderate</v>
       </c>
       <c r="L3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A4,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Software attacks</v>
+        <v>Information extortion</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C4,Assets!A:C,2,FALSE),"")</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="E4" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C4,Assets!A:C,3,FALSE),"")</f>
-        <v>Bank Account</v>
+        <v>PCs</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="str">
         <f t="shared" si="0"/>
-        <v>T2V2A1</v>
+        <v>T3V3A1</v>
       </c>
       <c r="H4" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="K4" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I4,"|",J4),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
+        <v>High</v>
       </c>
       <c r="L4">
-        <v>62</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A5,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
+        <v>Technical software failures or errors</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C5,Assets!A:C,2,FALSE),"")</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="E5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C5,Assets!A:C,3,FALSE),"")</f>
-        <v>Customer Data</v>
+        <v>Router</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="str">
         <f t="shared" si="0"/>
-        <v>T1V1A2</v>
+        <v>T9V1A2</v>
       </c>
       <c r="H5" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="I5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I5,"|",J5),RiskValues!C:D,2,FALSE),"")</f>
         <v>Low</v>
       </c>
       <c r="L5">
-        <v>79</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:14" s="23" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A6,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Theft</v>
+        <v>Espionage and trespass</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C6,Assets!A:C,2,FALSE),"")</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="E6" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C6,Assets!A:C,3,FALSE),"")</f>
-        <v>Customer Data</v>
+        <v>Router</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" t="str">
         <f t="shared" si="0"/>
-        <v>T5V2A2</v>
+        <v>T4V2A2</v>
       </c>
       <c r="H6" t="s">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="I6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K6" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I6,"|",J6),RiskValues!C:D,2,FALSE),"")</f>
         <v>Low</v>
       </c>
       <c r="L6">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="M6"/>
       <c r="N6"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B7" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A7,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Technical hardware failures or errors</v>
+        <v>Theft</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C7,Assets!A:C,2,FALSE),"")</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="E7" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C7,Assets!A:C,3,FALSE),"")</f>
-        <v>Customer Data</v>
+        <v>Router</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
-        <v>T8V3A2</v>
+        <v>T5V3A2</v>
       </c>
       <c r="H7" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="I7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J7" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K7" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I7,"|",J7),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Low</v>
+        <v>Moderate</v>
       </c>
       <c r="L7">
-        <v>78</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A8,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Forces of nature</v>
+        <v>Technical hardware failures or errors</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C8,Assets!A:C,2,FALSE),"")</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="E8" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C8,Assets!A:C,3,FALSE),"")</f>
-        <v>Customer Data</v>
+        <v>Switch</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G8" t="str">
         <f t="shared" si="0"/>
-        <v>T7V4A2</v>
+        <v>T8V1A3</v>
       </c>
       <c r="H8" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K8" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I8,"|",J8),RiskValues!C:D,2,FALSE),"")</f>
         <v>Low</v>
       </c>
       <c r="L8">
-        <v>77</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B9" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A9,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
+        <v>Espionage and trespass</v>
       </c>
       <c r="C9">
         <v>3</v>
       </c>
-      <c r="D9" t="s">
-        <v>31</v>
+      <c r="D9" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C9,Assets!A:C,2,FALSE),"")</f>
+        <v>Hardware</v>
       </c>
       <c r="E9" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C9,Assets!A:C,3,FALSE),"")</f>
-        <v>Employee data (HR records, payroll, personal information)</v>
+        <v>Switch</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="str">
         <f t="shared" si="0"/>
-        <v>T1V1A3</v>
+        <v>T4V2A3</v>
       </c>
       <c r="H9" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="I9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K9" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I9,"|",J9),RiskValues!C:D,2,FALSE),"")</f>
         <v>Moderate</v>
       </c>
       <c r="L9">
-        <v>61</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B10" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A10,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Software attacks</v>
+        <v>Sabotage and vandalism</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
-      <c r="D10" t="s">
-        <v>31</v>
+      <c r="D10" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C10,Assets!A:C,2,FALSE),"")</f>
+        <v>Hardware</v>
       </c>
       <c r="E10" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C10,Assets!A:C,3,FALSE),"")</f>
-        <v>Employee data (HR records, payroll, personal information)</v>
+        <v>Switch</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" t="str">
         <f t="shared" si="0"/>
-        <v>T2V2A3</v>
+        <v>T11V3A3</v>
       </c>
       <c r="H10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K10" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I10,"|",J10),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
+        <v>Very Low</v>
       </c>
       <c r="L10">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B11" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A11,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Theft</v>
+        <v>Software attacks</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C11,Assets!A:C,2,FALSE),"")</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="E11" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C11,Assets!A:C,3,FALSE),"")</f>
-        <v>Employee data (HR records, payroll, personal information)</v>
+        <v>Server / VM Host</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11" t="str">
         <f t="shared" si="0"/>
-        <v>T5V3A3</v>
+        <v>T2V1A4</v>
       </c>
       <c r="H11" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="I11" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J11" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K11" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I11,"|",J11),RiskValues!C:D,2,FALSE),"")</f>
         <v>Moderate</v>
       </c>
       <c r="L11">
-        <v>59</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B12" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A12,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Technical software failures or errors</v>
+        <v>People errors</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C12,Assets!A:C,2,FALSE),"")</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="E12" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C12,Assets!A:C,3,FALSE),"")</f>
-        <v>Employee data (HR records, payroll, personal information)</v>
+        <v>Server / VM Host</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G12" t="str">
         <f t="shared" si="0"/>
-        <v>T9V4A3</v>
+        <v>T1V2A4</v>
       </c>
       <c r="H12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J12" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K12" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I12,"|",J12),RiskValues!C:D,2,FALSE),"")</f>
         <v>Moderate</v>
       </c>
       <c r="L12">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B13" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A13,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
+        <v>Technological obsolescence</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C13,Assets!A:C,2,FALSE),"")</f>
-        <v>Data</v>
+        <v>Software</v>
       </c>
       <c r="E13" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C13,Assets!A:C,3,FALSE),"")</f>
-        <v>CRM</v>
+        <v>OpenWRT</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="0"/>
-        <v>T1V1A4</v>
+        <v>T6V1A5</v>
       </c>
       <c r="H13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I13" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K13" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I13,"|",J13),RiskValues!C:D,2,FALSE),"")</f>
         <v>Moderate</v>
       </c>
       <c r="L13">
-        <v>65</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B14" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A14,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Software attacks</v>
+        <v>Technical software failures or errors</v>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C14,Assets!A:C,2,FALSE),"")</f>
-        <v>Data</v>
+        <v>Software</v>
       </c>
       <c r="E14" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C14,Assets!A:C,3,FALSE),"")</f>
-        <v>CRM</v>
+        <v>OpenWRT</v>
       </c>
       <c r="F14">
         <v>2</v>
       </c>
       <c r="G14" t="str">
         <f t="shared" si="0"/>
-        <v>T2V2A4</v>
+        <v>T9V2A5</v>
       </c>
       <c r="H14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K14" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I14,"|",J14),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
+        <v>Low</v>
       </c>
       <c r="L14">
-        <v>58</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B15" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A15,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Technical software failures or errors</v>
+        <v>Software attacks</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D15" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C15,Assets!A:C,2,FALSE),"")</f>
-        <v>Data</v>
+        <v>Software</v>
       </c>
       <c r="E15" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C15,Assets!A:C,3,FALSE),"")</f>
-        <v>CRM</v>
+        <v>LuCI</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" t="str">
         <f t="shared" si="0"/>
-        <v>T9V3A4</v>
+        <v>T2V1A6</v>
       </c>
       <c r="H15" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I15" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J15" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K15" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I15,"|",J15),RiskValues!C:D,2,FALSE),"")</f>
         <v>Moderate</v>
       </c>
       <c r="L15">
-        <v>66</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A16,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>IP compromises</v>
+        <v>Software attacks</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C16,Assets!A:C,2,FALSE),"")</f>
-        <v>Data</v>
+        <v>Software</v>
       </c>
       <c r="E16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C16,Assets!A:C,3,FALSE),"")</f>
-        <v>CRM</v>
+        <v>Accounting Software</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G16" t="str">
         <f t="shared" si="0"/>
-        <v>T12V4A4</v>
+        <v>T2V1A7</v>
       </c>
       <c r="H16" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="I16" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J16" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="K16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I16,"|",J16),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
+        <v>High</v>
       </c>
       <c r="L16">
-        <v>57</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A17,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
+        <v>Software attacks</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D17" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C17,Assets!A:C,2,FALSE),"")</f>
-        <v>Data</v>
+        <v>Software</v>
       </c>
       <c r="E17" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C17,Assets!A:C,3,FALSE),"")</f>
-        <v>Financial data (accounting records, invoices, tax data)</v>
+        <v xml:space="preserve">Dropbear SSH </v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" si="0"/>
-        <v>T1V1A5</v>
+        <v>T2V1A8</v>
       </c>
       <c r="H17" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K17" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I17,"|",J17),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Very High</v>
+        <v>Moderate</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A18,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Software attacks</v>
+        <v>People errors</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D18" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C18,Assets!A:C,2,FALSE),"")</f>
-        <v>Data</v>
+        <v>People</v>
       </c>
       <c r="E18" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C18,Assets!A:C,3,FALSE),"")</f>
-        <v>Financial data (accounting records, invoices, tax data)</v>
+        <v>Manager</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" t="str">
         <f t="shared" si="0"/>
-        <v>T2V2A5</v>
+        <v>T1V1A9</v>
       </c>
       <c r="H18" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I18" t="s">
         <v>47</v>
@@ -2665,96 +2423,96 @@
       </c>
       <c r="K18" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I18,"|",J18),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Very High</v>
+        <v>Low</v>
       </c>
       <c r="L18">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B19" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A19,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Information extortion</v>
+        <v>People errors</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D19" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C19,Assets!A:C,2,FALSE),"")</f>
-        <v>Data</v>
+        <v>People</v>
       </c>
       <c r="E19" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C19,Assets!A:C,3,FALSE),"")</f>
-        <v>Financial data (accounting records, invoices, tax data)</v>
+        <v>Accountants</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="0"/>
-        <v>T3V3A5</v>
+        <v>T1V1A10</v>
       </c>
       <c r="H19" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="I19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K19" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I19,"|",J19),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Very High</v>
+        <v>Moderate</v>
       </c>
       <c r="L19">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B20" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A20,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Technical hardware failures or errors</v>
+        <v>People errors</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D20" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C20,Assets!A:C,2,FALSE),"")</f>
-        <v>Data</v>
+        <v>People</v>
       </c>
       <c r="E20" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C20,Assets!A:C,3,FALSE),"")</f>
-        <v>Financial data (accounting records, invoices, tax data)</v>
+        <v>Bookkeeper</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G20" t="str">
         <f t="shared" si="0"/>
-        <v>T8V4A5</v>
+        <v>T1V1A11</v>
       </c>
       <c r="H20" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="I20" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K20" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I20,"|",J20),RiskValues!C:D,2,FALSE),"")</f>
-        <v>High</v>
+        <v>Moderate</v>
       </c>
       <c r="L20">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -2766,466 +2524,468 @@
         <v>People errors</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D21" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C21,Assets!A:C,2,FALSE),"")</f>
-        <v>Hardware</v>
+        <v>People</v>
       </c>
       <c r="E21" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C21,Assets!A:C,3,FALSE),"")</f>
-        <v>Backup Data</v>
+        <v>IT Support worker</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" t="str">
         <f t="shared" si="0"/>
-        <v>T1V1A6</v>
+        <v>T1V1A12</v>
       </c>
       <c r="H21" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I21" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J21" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K21" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I21,"|",J21),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
+        <v>Low</v>
       </c>
       <c r="L21">
-        <v>56</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B22" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A22,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Theft</v>
+        <v>Changing quality of services</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D22" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C22,Assets!A:C,2,FALSE),"")</f>
-        <v>Hardware</v>
+        <v>Network</v>
       </c>
       <c r="E22" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C22,Assets!A:C,3,FALSE),"")</f>
-        <v>Backup Data</v>
+        <v>LAN 88.1.1.0/24</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" t="str">
         <f t="shared" si="0"/>
-        <v>T5V2A6</v>
+        <v>T10V1A13</v>
       </c>
       <c r="H22" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I22" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K22" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I22,"|",J22),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
+        <v>Low</v>
       </c>
       <c r="L22">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A23,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Information extortion</v>
+        <v>Software attacks</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D23" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C23,Assets!A:C,2,FALSE),"")</f>
-        <v>Hardware</v>
+        <v>Network</v>
       </c>
       <c r="E23" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C23,Assets!A:C,3,FALSE),"")</f>
-        <v>Backup Data</v>
+        <v>VM network 192.168.56.0/24</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23" t="str">
         <f t="shared" si="0"/>
-        <v>T3V3A6</v>
+        <v>T2V1A14</v>
       </c>
       <c r="H23" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I23" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K23" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I23,"|",J23),RiskValues!C:D,2,FALSE),"")</f>
         <v>High</v>
       </c>
       <c r="L23">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B24" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A24,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Forces of nature</v>
+        <v>People errors</v>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D24" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C24,Assets!A:C,2,FALSE),"")</f>
-        <v>Hardware</v>
+        <v>Network</v>
       </c>
       <c r="E24" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C24,Assets!A:C,3,FALSE),"")</f>
-        <v>Backup Data</v>
+        <v>WAN Connection 10.0.3.15/24</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24" t="str">
         <f t="shared" si="0"/>
-        <v>T7V4A6</v>
+        <v>T1V3A15</v>
       </c>
       <c r="H24" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I24" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J24" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K24" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I24,"|",J24),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
+        <v>High</v>
       </c>
       <c r="L24">
-        <v>55</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B25" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A25,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
+        <v>Information extortion</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D25" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C25,Assets!A:C,2,FALSE),"")</f>
-        <v>Hardware</v>
+        <v>Data</v>
       </c>
       <c r="E25" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C25,Assets!A:C,3,FALSE),"")</f>
-        <v>Routers and firewalls</v>
+        <v>Client Tax Records</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="0"/>
-        <v>T1V1A7</v>
+        <v>T3V1A16</v>
       </c>
       <c r="H25" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="I25" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J25" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="K25" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I25,"|",J25),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
+        <v>Very High</v>
       </c>
       <c r="L25">
-        <v>54</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B26" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A26,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Software attacks</v>
+        <v>People errors</v>
       </c>
       <c r="C26">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D26" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C26,Assets!A:C,2,FALSE),"")</f>
-        <v>Hardware</v>
+        <v>Data</v>
       </c>
       <c r="E26" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C26,Assets!A:C,3,FALSE),"")</f>
-        <v>Routers and firewalls</v>
+        <v>Payroll Data</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" t="str">
         <f t="shared" si="0"/>
-        <v>T2V2A7</v>
+        <v>T1V1A17</v>
       </c>
       <c r="H26" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J26" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="K26" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I26,"|",J26),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Very High</v>
+        <v>High</v>
       </c>
       <c r="L26">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B27" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A27,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Technical hardware failures or errors</v>
+        <v>Software attacks</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D27" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C27,Assets!A:C,2,FALSE),"")</f>
-        <v>Hardware</v>
+        <v>Data</v>
       </c>
       <c r="E27" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C27,Assets!A:C,3,FALSE),"")</f>
-        <v>Routers and firewalls</v>
+        <v>Financial Statements</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27" t="str">
         <f t="shared" si="0"/>
-        <v>T8V3A7</v>
+        <v>T2V1A18</v>
       </c>
       <c r="H27" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="I27" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K27" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I27,"|",J27),RiskValues!C:D,2,FALSE),"")</f>
-        <v>High</v>
+        <v>Moderate</v>
       </c>
       <c r="L27">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B28" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A28,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Theft</v>
+        <v>Sabotage and vandalism</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D28" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C28,Assets!A:C,2,FALSE),"")</f>
-        <v>Hardware</v>
+        <v>Data</v>
       </c>
       <c r="E28" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C28,Assets!A:C,3,FALSE),"")</f>
-        <v>Routers and firewalls</v>
+        <v>Website content</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G28" t="str">
         <f t="shared" si="0"/>
-        <v>T5V4A7</v>
+        <v>T11V1A19</v>
       </c>
       <c r="H28" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="I28" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K28" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I28,"|",J28),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Very High</v>
+        <v>Moderate</v>
       </c>
       <c r="L28">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>1</v>
       </c>
-      <c r="B29" t="s">
-        <v>3</v>
+      <c r="B29" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A29,InfoSecThreats!A:B,2,FALSE),"")</f>
+        <v>People errors</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D29" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C29,Assets!A:C,2,FALSE),"")</f>
-        <v>Hardware</v>
+        <v>Processes</v>
       </c>
       <c r="E29" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C29,Assets!A:C,3,FALSE),"")</f>
-        <v>Switch</v>
+        <v>Firewall management</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29" t="str">
         <f t="shared" si="0"/>
-        <v>T1V1A8</v>
+        <v>T1V1A20</v>
       </c>
       <c r="H29" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="I29" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J29" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K29" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I29,"|",J29),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="L29">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>4</v>
       </c>
-      <c r="B30" t="s">
-        <v>6</v>
+      <c r="B30" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(A30,InfoSecThreats!A:B,2,FALSE),"")</f>
+        <v>Espionage and trespass</v>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D30" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C30,Assets!A:C,2,FALSE),"")</f>
-        <v>Hardware</v>
+        <v>Processes</v>
       </c>
       <c r="E30" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C30,Assets!A:C,3,FALSE),"")</f>
-        <v>Switch</v>
+        <v>Access to the SSH server</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" t="str">
         <f t="shared" si="0"/>
-        <v>T4V2A8</v>
+        <v>T4V1A21</v>
       </c>
       <c r="H30" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="I30" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J30" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="K30" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I30,"|",J30),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
+        <v>High</v>
       </c>
       <c r="L30">
-        <v>53</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B31" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A31,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Sabotage and vandalism</v>
+        <v>Technical software failures or errors</v>
       </c>
       <c r="C31">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D31" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C31,Assets!A:C,2,FALSE),"")</f>
-        <v>Hardware</v>
+        <v>Processes</v>
       </c>
       <c r="E31" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C31,Assets!A:C,3,FALSE),"")</f>
-        <v>Switch</v>
+        <v>Backup procedure</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="0"/>
-        <v>T11V3A8</v>
+        <v>T9V1A22</v>
       </c>
       <c r="H31" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="I31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J31" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K31" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I31,"|",J31),RiskValues!C:D,2,FALSE),"")</f>
         <v>Moderate</v>
       </c>
       <c r="L31">
-        <v>67</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -3237,2363 +2997,1229 @@
         <v>Theft</v>
       </c>
       <c r="C32">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D32" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C32,Assets!A:C,2,FALSE),"")</f>
-        <v>Hardware</v>
+        <v>Processes</v>
       </c>
       <c r="E32" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C32,Assets!A:C,3,FALSE),"")</f>
-        <v xml:space="preserve">Desktop computers and laptops </v>
+        <v>Backup procedure</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" t="str">
         <f t="shared" si="0"/>
-        <v>T5V1A9</v>
+        <v>T5V2A22</v>
       </c>
       <c r="H32" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="I32" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J32" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="K32" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I32,"|",J32),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
+        <v>Very High</v>
       </c>
       <c r="L32">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33">
         <v>2</v>
       </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A33,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Software attacks</v>
-      </c>
-      <c r="C33">
-        <v>9</v>
+        <v/>
       </c>
       <c r="D33" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C33,Assets!A:C,2,FALSE),"")</f>
-        <v>Hardware</v>
+        <v/>
       </c>
       <c r="E33" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C33,Assets!A:C,3,FALSE),"")</f>
-        <v xml:space="preserve">Desktop computers and laptops </v>
-      </c>
-      <c r="F33">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G33" t="str">
         <f t="shared" si="0"/>
-        <v>T2V2A9</v>
-      </c>
-      <c r="H33" t="s">
-        <v>119</v>
-      </c>
-      <c r="I33" t="s">
-        <v>48</v>
-      </c>
-      <c r="J33" t="s">
-        <v>48</v>
+        <v/>
       </c>
       <c r="K33" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I33,"|",J33),RiskValues!C:D,2,FALSE),"")</f>
-        <v>High</v>
-      </c>
-      <c r="L33">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>5</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A34,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Theft</v>
-      </c>
-      <c r="C34">
-        <v>10</v>
+        <v/>
       </c>
       <c r="D34" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C34,Assets!A:C,2,FALSE),"")</f>
-        <v>Hardware</v>
+        <v/>
       </c>
       <c r="E34" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C34,Assets!A:C,3,FALSE),"")</f>
-        <v>Printers and scanners</v>
-      </c>
-      <c r="F34">
-        <v>3</v>
+        <v/>
       </c>
       <c r="G34" t="str">
         <f t="shared" si="0"/>
-        <v>T5V3A10</v>
-      </c>
-      <c r="H34" t="s">
-        <v>103</v>
-      </c>
-      <c r="I34" t="s">
-        <v>49</v>
-      </c>
-      <c r="J34" t="s">
-        <v>50</v>
+        <v/>
       </c>
       <c r="K34" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I34,"|",J34),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Low</v>
-      </c>
-      <c r="L34">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>7</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A35,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Forces of nature</v>
-      </c>
-      <c r="C35">
-        <v>11</v>
+        <v/>
       </c>
       <c r="D35" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C35,Assets!A:C,2,FALSE),"")</f>
-        <v>Hardware</v>
+        <v/>
       </c>
       <c r="E35" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C35,Assets!A:C,3,FALSE),"")</f>
-        <v>Uninterruptible Power Supplies (UPS)</v>
-      </c>
-      <c r="F35">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G35" t="str">
-        <f t="shared" si="0"/>
-        <v>T7V1A11</v>
-      </c>
-      <c r="H35" t="s">
-        <v>120</v>
-      </c>
-      <c r="I35" t="s">
-        <v>50</v>
-      </c>
-      <c r="J35" t="s">
-        <v>48</v>
+        <f>IF(ISBLANK(F35),"",_xlfn.CONCAT("T",A35,"V",F35,"A",C35))</f>
+        <v/>
       </c>
       <c r="K35" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I35,"|",J35),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Low</v>
-      </c>
-      <c r="L35">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>5</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A36,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Theft</v>
-      </c>
-      <c r="C36">
-        <v>11</v>
+        <v/>
       </c>
       <c r="D36" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C36,Assets!A:C,2,FALSE),"")</f>
-        <v>Hardware</v>
+        <v/>
       </c>
       <c r="E36" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C36,Assets!A:C,3,FALSE),"")</f>
-        <v>Uninterruptible Power Supplies (UPS)</v>
-      </c>
-      <c r="F36">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G36" t="str">
-        <f>IF(ISBLANK(F36),"",_xlfn.CONCAT("T",A36,"V",F36,"A",C36))</f>
-        <v>T5V2A11</v>
-      </c>
-      <c r="H36" t="s">
-        <v>121</v>
-      </c>
-      <c r="I36" t="s">
-        <v>51</v>
-      </c>
-      <c r="J36" t="s">
-        <v>48</v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K36" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I36,"|",J36),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Low</v>
-      </c>
-      <c r="L36">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>5</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A37,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Theft</v>
-      </c>
-      <c r="C37">
-        <v>12</v>
+        <v/>
       </c>
       <c r="D37" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C37,Assets!A:C,2,FALSE),"")</f>
-        <v>Hardware</v>
+        <v/>
       </c>
       <c r="E37" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C37,Assets!A:C,3,FALSE),"")</f>
-        <v>Racks, cabling (Ethernet, fibre), patch panels</v>
-      </c>
-      <c r="F37">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G37" t="str">
         <f t="shared" si="0"/>
-        <v>T5V1A12</v>
-      </c>
-      <c r="H37" t="s">
-        <v>121</v>
-      </c>
-      <c r="I37" t="s">
-        <v>48</v>
-      </c>
-      <c r="J37" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K37" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I37,"|",J37),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Very High</v>
-      </c>
-      <c r="L37">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>7</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A38,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Forces of nature</v>
-      </c>
-      <c r="C38">
-        <v>12</v>
+        <v/>
       </c>
       <c r="D38" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C38,Assets!A:C,2,FALSE),"")</f>
-        <v>Hardware</v>
+        <v/>
       </c>
       <c r="E38" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C38,Assets!A:C,3,FALSE),"")</f>
-        <v>Racks, cabling (Ethernet, fibre), patch panels</v>
-      </c>
-      <c r="F38">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G38" t="str">
         <f t="shared" si="0"/>
-        <v>T7V2A12</v>
-      </c>
-      <c r="H38" t="s">
-        <v>122</v>
-      </c>
-      <c r="I38" t="s">
-        <v>49</v>
-      </c>
-      <c r="J38" t="s">
-        <v>48</v>
+        <v/>
       </c>
       <c r="K38" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I38,"|",J38),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
-      </c>
-      <c r="L38">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>6</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A39,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Technological obsolescence</v>
-      </c>
-      <c r="C39">
-        <v>12</v>
+        <v/>
       </c>
       <c r="D39" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C39,Assets!A:C,2,FALSE),"")</f>
-        <v>Hardware</v>
+        <v/>
       </c>
       <c r="E39" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C39,Assets!A:C,3,FALSE),"")</f>
-        <v>Racks, cabling (Ethernet, fibre), patch panels</v>
-      </c>
-      <c r="F39">
-        <v>3</v>
+        <v/>
       </c>
       <c r="G39" t="str">
         <f t="shared" si="0"/>
-        <v>T6V3A12</v>
-      </c>
-      <c r="H39" t="s">
-        <v>123</v>
-      </c>
-      <c r="I39" t="s">
-        <v>50</v>
-      </c>
-      <c r="J39" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K39" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I39,"|",J39),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
-      </c>
-      <c r="L39">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>4</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A40,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Espionage and trespass</v>
-      </c>
-      <c r="C40">
-        <v>13</v>
+        <v/>
       </c>
       <c r="D40" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C40,Assets!A:C,2,FALSE),"")</f>
-        <v>Software</v>
+        <v/>
       </c>
       <c r="E40" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C40,Assets!A:C,3,FALSE),"")</f>
-        <v>Operating systems (Windows Server, Linux, Windows/macOS clients)</v>
-      </c>
-      <c r="F40">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G40" t="str">
         <f t="shared" si="0"/>
-        <v>T4V1A13</v>
-      </c>
-      <c r="H40" t="s">
-        <v>124</v>
-      </c>
-      <c r="I40" t="s">
-        <v>47</v>
-      </c>
-      <c r="J40" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K40" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I40,"|",J40),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Very High</v>
-      </c>
-      <c r="L40">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>2</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A41,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Software attacks</v>
-      </c>
-      <c r="C41">
-        <v>13</v>
+        <v/>
       </c>
       <c r="D41" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C41,Assets!A:C,2,FALSE),"")</f>
-        <v>Software</v>
+        <v/>
       </c>
       <c r="E41" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C41,Assets!A:C,3,FALSE),"")</f>
-        <v>Operating systems (Windows Server, Linux, Windows/macOS clients)</v>
-      </c>
-      <c r="F41">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G41" t="str">
         <f t="shared" si="0"/>
-        <v>T2V2A13</v>
-      </c>
-      <c r="H41" t="s">
-        <v>87</v>
-      </c>
-      <c r="I41" t="s">
-        <v>48</v>
-      </c>
-      <c r="J41" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K41" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I41,"|",J41),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Very High</v>
-      </c>
-      <c r="L41">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>5</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A42,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Theft</v>
-      </c>
-      <c r="C42">
-        <v>14</v>
+        <v/>
       </c>
       <c r="D42" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C42,Assets!A:C,2,FALSE),"")</f>
-        <v>Software</v>
+        <v/>
       </c>
       <c r="E42" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C42,Assets!A:C,3,FALSE),"")</f>
-        <v>Accounting and finance software</v>
-      </c>
-      <c r="F42">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G42" t="str">
         <f t="shared" si="0"/>
-        <v>T5V1A14</v>
-      </c>
-      <c r="H42" t="s">
-        <v>105</v>
-      </c>
-      <c r="I42" t="s">
-        <v>49</v>
-      </c>
-      <c r="J42" t="s">
-        <v>48</v>
+        <v/>
       </c>
       <c r="K42" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I42,"|",J42),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
-      </c>
-      <c r="L42">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>5</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A43,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Theft</v>
-      </c>
-      <c r="C43">
-        <v>15</v>
+        <v/>
       </c>
       <c r="D43" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C43,Assets!A:C,2,FALSE),"")</f>
-        <v>Software</v>
+        <v/>
       </c>
       <c r="E43" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C43,Assets!A:C,3,FALSE),"")</f>
-        <v>Security software (antivirus, endpoint protection)</v>
-      </c>
-      <c r="F43">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G43" t="str">
         <f t="shared" si="0"/>
-        <v>T5V1A15</v>
-      </c>
-      <c r="H43" t="s">
-        <v>104</v>
-      </c>
-      <c r="I43" t="s">
-        <v>49</v>
-      </c>
-      <c r="J43" t="s">
-        <v>48</v>
+        <v/>
       </c>
       <c r="K43" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I43,"|",J43),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
-      </c>
-      <c r="L43">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>2</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A44,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Software attacks</v>
-      </c>
-      <c r="C44">
-        <v>16</v>
+        <v/>
       </c>
       <c r="D44" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C44,Assets!A:C,2,FALSE),"")</f>
-        <v>Software</v>
+        <v/>
       </c>
       <c r="E44" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C44,Assets!A:C,3,FALSE),"")</f>
-        <v>Website and web applications</v>
-      </c>
-      <c r="F44">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G44" t="str">
         <f t="shared" si="0"/>
-        <v>T2V1A16</v>
-      </c>
-      <c r="H44" t="s">
-        <v>125</v>
-      </c>
-      <c r="I44" t="s">
-        <v>48</v>
-      </c>
-      <c r="J44" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K44" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I44,"|",J44),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Very High</v>
-      </c>
-      <c r="L44">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>9</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A45,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Technical software failures or errors</v>
-      </c>
-      <c r="C45">
-        <v>16</v>
+        <v/>
       </c>
       <c r="D45" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C45,Assets!A:C,2,FALSE),"")</f>
-        <v>Software</v>
+        <v/>
       </c>
       <c r="E45" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C45,Assets!A:C,3,FALSE),"")</f>
-        <v>Website and web applications</v>
-      </c>
-      <c r="F45">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G45" t="str">
         <f t="shared" si="0"/>
-        <v>T9V2A16</v>
-      </c>
-      <c r="H45" t="s">
-        <v>126</v>
-      </c>
-      <c r="I45" t="s">
-        <v>49</v>
-      </c>
-      <c r="J45" t="s">
-        <v>48</v>
+        <v/>
       </c>
       <c r="K45" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I45,"|",J45),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
-      </c>
-      <c r="L45">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>2</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A46,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Software attacks</v>
-      </c>
-      <c r="C46">
-        <v>17</v>
+        <v/>
       </c>
       <c r="D46" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C46,Assets!A:C,2,FALSE),"")</f>
-        <v>Software</v>
+        <v/>
       </c>
       <c r="E46" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C46,Assets!A:C,3,FALSE),"")</f>
-        <v>CRM software</v>
-      </c>
-      <c r="F46">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G46" t="str">
         <f t="shared" si="0"/>
-        <v>T2V1A17</v>
-      </c>
-      <c r="H46" t="s">
-        <v>127</v>
-      </c>
-      <c r="I46" t="s">
-        <v>48</v>
-      </c>
-      <c r="J46" t="s">
-        <v>48</v>
+        <v/>
       </c>
       <c r="K46" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I46,"|",J46),RiskValues!C:D,2,FALSE),"")</f>
-        <v>High</v>
-      </c>
-      <c r="L46">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A47,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
-      </c>
-      <c r="C47">
-        <v>17</v>
+        <v/>
       </c>
       <c r="D47" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C47,Assets!A:C,2,FALSE),"")</f>
-        <v>Software</v>
+        <v/>
       </c>
       <c r="E47" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C47,Assets!A:C,3,FALSE),"")</f>
-        <v>CRM software</v>
-      </c>
-      <c r="F47">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G47" t="str">
         <f t="shared" si="0"/>
-        <v>T1V2A17</v>
-      </c>
-      <c r="H47" t="s">
-        <v>128</v>
-      </c>
-      <c r="I47" t="s">
-        <v>49</v>
-      </c>
-      <c r="J47" t="s">
-        <v>49</v>
+        <v/>
       </c>
       <c r="K47" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I47,"|",J47),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
-      </c>
-      <c r="L47">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>9</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A48,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Technical software failures or errors</v>
-      </c>
-      <c r="C48">
-        <v>17</v>
+        <v/>
       </c>
       <c r="D48" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C48,Assets!A:C,2,FALSE),"")</f>
-        <v>Software</v>
+        <v/>
       </c>
       <c r="E48" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C48,Assets!A:C,3,FALSE),"")</f>
-        <v>CRM software</v>
-      </c>
-      <c r="F48">
-        <v>3</v>
+        <v/>
       </c>
       <c r="G48" t="str">
         <f t="shared" si="0"/>
-        <v>T9V3A17</v>
-      </c>
-      <c r="H48" t="s">
-        <v>129</v>
-      </c>
-      <c r="I48" t="s">
-        <v>49</v>
-      </c>
-      <c r="J48" t="s">
-        <v>48</v>
+        <v/>
       </c>
       <c r="K48" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I48,"|",J48),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
-      </c>
-      <c r="L48">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>9</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A49,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Technical software failures or errors</v>
-      </c>
-      <c r="C49">
-        <v>18</v>
+        <v/>
       </c>
       <c r="D49" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C49,Assets!A:C,2,FALSE),"")</f>
-        <v>Software</v>
+        <v/>
       </c>
       <c r="E49" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C49,Assets!A:C,3,FALSE),"")</f>
-        <v>Security software (antivirus, endpoint protection)</v>
-      </c>
-      <c r="F49">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G49" t="str">
         <f t="shared" si="0"/>
-        <v>T9V1A18</v>
-      </c>
-      <c r="H49" t="s">
-        <v>131</v>
-      </c>
-      <c r="I49" t="s">
-        <v>49</v>
-      </c>
-      <c r="J49" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K49" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I49,"|",J49),RiskValues!C:D,2,FALSE),"")</f>
-        <v>High</v>
-      </c>
-      <c r="L49">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>6</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A50,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Technological obsolescence</v>
-      </c>
-      <c r="C50">
-        <v>18</v>
+        <v/>
       </c>
       <c r="D50" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C50,Assets!A:C,2,FALSE),"")</f>
-        <v>Software</v>
+        <v/>
       </c>
       <c r="E50" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C50,Assets!A:C,3,FALSE),"")</f>
-        <v>Security software (antivirus, endpoint protection)</v>
-      </c>
-      <c r="F50">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G50" t="str">
         <f t="shared" si="0"/>
-        <v>T6V2A18</v>
-      </c>
-      <c r="H50" t="s">
-        <v>130</v>
-      </c>
-      <c r="I50" t="s">
-        <v>49</v>
-      </c>
-      <c r="J50" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K50" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I50,"|",J50),RiskValues!C:D,2,FALSE),"")</f>
-        <v>High</v>
-      </c>
-      <c r="L50">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A51,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
-      </c>
-      <c r="C51">
-        <v>19</v>
+        <v/>
       </c>
       <c r="D51" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C51,Assets!A:C,2,FALSE),"")</f>
-        <v>Network</v>
+        <v/>
       </c>
       <c r="E51" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C51,Assets!A:C,3,FALSE),"")</f>
-        <v>Network management and monitoring tools</v>
-      </c>
-      <c r="F51">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G51" t="str">
         <f t="shared" si="0"/>
-        <v>T1V1A19</v>
-      </c>
-      <c r="H51" t="s">
-        <v>132</v>
-      </c>
-      <c r="I51" t="s">
-        <v>48</v>
-      </c>
-      <c r="J51" t="s">
-        <v>48</v>
+        <v/>
       </c>
       <c r="K51" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I51,"|",J51),RiskValues!C:D,2,FALSE),"")</f>
-        <v>High</v>
-      </c>
-      <c r="L51">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>2</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A52,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Software attacks</v>
-      </c>
-      <c r="C52">
-        <v>19</v>
+        <v/>
       </c>
       <c r="D52" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C52,Assets!A:C,2,FALSE),"")</f>
-        <v>Network</v>
+        <v/>
       </c>
       <c r="E52" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C52,Assets!A:C,3,FALSE),"")</f>
-        <v>Network management and monitoring tools</v>
-      </c>
-      <c r="F52">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G52" t="str">
         <f t="shared" si="0"/>
-        <v>T2V2A19</v>
-      </c>
-      <c r="H52" t="s">
-        <v>133</v>
-      </c>
-      <c r="I52" t="s">
-        <v>48</v>
-      </c>
-      <c r="J52" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K52" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I52,"|",J52),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Very High</v>
-      </c>
-      <c r="L52">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>8</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A53,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Technical hardware failures or errors</v>
-      </c>
-      <c r="C53">
-        <v>19</v>
+        <v/>
       </c>
       <c r="D53" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C53,Assets!A:C,2,FALSE),"")</f>
-        <v>Network</v>
+        <v/>
       </c>
       <c r="E53" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C53,Assets!A:C,3,FALSE),"")</f>
-        <v>Network management and monitoring tools</v>
-      </c>
-      <c r="F53">
-        <v>3</v>
+        <v/>
       </c>
       <c r="G53" t="str">
         <f t="shared" si="0"/>
-        <v>T8V3A19</v>
-      </c>
-      <c r="H53" t="s">
-        <v>134</v>
-      </c>
-      <c r="I53" t="s">
-        <v>49</v>
-      </c>
-      <c r="J53" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K53" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I53,"|",J53),RiskValues!C:D,2,FALSE),"")</f>
-        <v>High</v>
-      </c>
-      <c r="L53">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>10</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A54,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Changing quality of services</v>
-      </c>
-      <c r="C54">
-        <v>20</v>
+        <v/>
       </c>
       <c r="D54" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C54,Assets!A:C,2,FALSE),"")</f>
-        <v>Network</v>
+        <v/>
       </c>
       <c r="E54" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C54,Assets!A:C,3,FALSE),"")</f>
-        <v>Internet connections (ISP)</v>
-      </c>
-      <c r="F54">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G54" t="str">
         <f t="shared" si="0"/>
-        <v>T10V1A20</v>
-      </c>
-      <c r="H54" t="s">
-        <v>136</v>
-      </c>
-      <c r="I54" t="s">
-        <v>49</v>
-      </c>
-      <c r="J54" t="s">
-        <v>48</v>
+        <v/>
       </c>
       <c r="K54" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I54,"|",J54),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
-      </c>
-      <c r="L54">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>8</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A55,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Technical hardware failures or errors</v>
-      </c>
-      <c r="C55">
-        <v>20</v>
+        <v/>
       </c>
       <c r="D55" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C55,Assets!A:C,2,FALSE),"")</f>
-        <v>Network</v>
+        <v/>
       </c>
       <c r="E55" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C55,Assets!A:C,3,FALSE),"")</f>
-        <v>Internet connections (ISP)</v>
-      </c>
-      <c r="F55">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G55" t="str">
         <f t="shared" si="0"/>
-        <v>T8V2A20</v>
-      </c>
-      <c r="H55" t="s">
-        <v>135</v>
-      </c>
-      <c r="I55" t="s">
-        <v>50</v>
-      </c>
-      <c r="J55" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K55" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I55,"|",J55),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
-      </c>
-      <c r="L55">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A56,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
-      </c>
-      <c r="C56">
-        <v>21</v>
+        <v/>
       </c>
       <c r="D56" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C56,Assets!A:C,2,FALSE),"")</f>
-        <v>Network</v>
+        <v/>
       </c>
       <c r="E56" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C56,Assets!A:C,3,FALSE),"")</f>
-        <v>Firewalls and security gateways</v>
-      </c>
-      <c r="F56">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G56" t="str">
         <f t="shared" si="0"/>
-        <v>T1V1A21</v>
-      </c>
-      <c r="H56" t="s">
-        <v>137</v>
-      </c>
-      <c r="I56" t="s">
-        <v>49</v>
-      </c>
-      <c r="J56" t="s">
-        <v>49</v>
+        <v/>
       </c>
       <c r="K56" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I56,"|",J56),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
-      </c>
-      <c r="L56">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>2</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A57,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Software attacks</v>
-      </c>
-      <c r="C57">
-        <v>21</v>
+        <v/>
       </c>
       <c r="D57" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C57,Assets!A:C,2,FALSE),"")</f>
-        <v>Network</v>
+        <v/>
       </c>
       <c r="E57" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C57,Assets!A:C,3,FALSE),"")</f>
-        <v>Firewalls and security gateways</v>
-      </c>
-      <c r="F57">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G57" t="str">
         <f t="shared" si="0"/>
-        <v>T2V2A21</v>
-      </c>
-      <c r="H57" t="s">
-        <v>138</v>
-      </c>
-      <c r="I57" t="s">
-        <v>48</v>
-      </c>
-      <c r="J57" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K57" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I57,"|",J57),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Very High</v>
-      </c>
-      <c r="L57">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>8</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A58,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Technical hardware failures or errors</v>
-      </c>
-      <c r="C58">
-        <v>21</v>
+        <v/>
       </c>
       <c r="D58" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C58,Assets!A:C,2,FALSE),"")</f>
-        <v>Network</v>
+        <v/>
       </c>
       <c r="E58" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C58,Assets!A:C,3,FALSE),"")</f>
-        <v>Firewalls and security gateways</v>
-      </c>
-      <c r="F58">
-        <v>3</v>
+        <v/>
       </c>
       <c r="G58" t="str">
         <f t="shared" si="0"/>
-        <v>T8V3A21</v>
-      </c>
-      <c r="H58" t="s">
-        <v>139</v>
-      </c>
-      <c r="I58" t="s">
-        <v>49</v>
-      </c>
-      <c r="J58" t="s">
-        <v>50</v>
+        <v/>
       </c>
       <c r="K58" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I58,"|",J58),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Low</v>
-      </c>
-      <c r="L58">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>4</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A59,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Espionage and trespass</v>
-      </c>
-      <c r="C59">
-        <v>22</v>
+        <v/>
       </c>
       <c r="D59" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C59,Assets!A:C,2,FALSE),"")</f>
-        <v>Network</v>
+        <v/>
       </c>
       <c r="E59" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C59,Assets!A:C,3,FALSE),"")</f>
-        <v>Wireless networks</v>
-      </c>
-      <c r="F59">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G59" t="str">
         <f t="shared" si="0"/>
-        <v>T4V1A22</v>
-      </c>
-      <c r="H59" t="s">
-        <v>140</v>
-      </c>
-      <c r="I59" t="s">
-        <v>48</v>
-      </c>
-      <c r="J59" t="s">
-        <v>48</v>
+        <v/>
       </c>
       <c r="K59" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I59,"|",J59),RiskValues!C:D,2,FALSE),"")</f>
-        <v>High</v>
-      </c>
-      <c r="L59">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A60,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
-      </c>
-      <c r="C60">
-        <v>22</v>
+        <v/>
       </c>
       <c r="D60" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C60,Assets!A:C,2,FALSE),"")</f>
-        <v>Network</v>
+        <v/>
       </c>
       <c r="E60" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C60,Assets!A:C,3,FALSE),"")</f>
-        <v>Wireless networks</v>
-      </c>
-      <c r="F60">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G60" t="str">
         <f t="shared" si="0"/>
-        <v>T1V2A22</v>
-      </c>
-      <c r="H60" t="s">
-        <v>141</v>
-      </c>
-      <c r="I60" t="s">
-        <v>47</v>
-      </c>
-      <c r="J60" t="s">
-        <v>48</v>
+        <v/>
       </c>
       <c r="K60" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I60,"|",J60),RiskValues!C:D,2,FALSE),"")</f>
-        <v>High</v>
-      </c>
-      <c r="L60">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>2</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A61,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Software attacks</v>
-      </c>
-      <c r="C61">
-        <v>22</v>
+        <v/>
       </c>
       <c r="D61" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C61,Assets!A:C,2,FALSE),"")</f>
-        <v>Network</v>
+        <v/>
       </c>
       <c r="E61" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C61,Assets!A:C,3,FALSE),"")</f>
-        <v>Wireless networks</v>
-      </c>
-      <c r="F61">
-        <v>3</v>
+        <v/>
       </c>
       <c r="G61" t="str">
         <f t="shared" si="0"/>
-        <v>T2V3A22</v>
-      </c>
-      <c r="H61" t="s">
-        <v>142</v>
-      </c>
-      <c r="I61" t="s">
-        <v>49</v>
-      </c>
-      <c r="J61" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K61" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I61,"|",J61),RiskValues!C:D,2,FALSE),"")</f>
-        <v>High</v>
-      </c>
-      <c r="L61">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A62,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
-      </c>
-      <c r="C62">
-        <v>23</v>
+        <v/>
       </c>
       <c r="D62" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C62,Assets!A:C,2,FALSE),"")</f>
-        <v>Network</v>
+        <v/>
       </c>
       <c r="E62" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C62,Assets!A:C,3,FALSE),"")</f>
-        <v>Network addressing</v>
-      </c>
-      <c r="F62">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G62" t="str">
         <f t="shared" si="0"/>
-        <v>T1V1A23</v>
-      </c>
-      <c r="H62" t="s">
-        <v>143</v>
-      </c>
-      <c r="I62" t="s">
-        <v>49</v>
-      </c>
-      <c r="J62" t="s">
-        <v>48</v>
+        <v/>
       </c>
       <c r="K62" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I62,"|",J62),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
-      </c>
-      <c r="L62">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>9</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A63,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Technical software failures or errors</v>
-      </c>
-      <c r="C63">
-        <v>23</v>
+        <v/>
       </c>
       <c r="D63" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C63,Assets!A:C,2,FALSE),"")</f>
-        <v>Network</v>
+        <v/>
       </c>
       <c r="E63" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C63,Assets!A:C,3,FALSE),"")</f>
-        <v>Network addressing</v>
-      </c>
-      <c r="F63">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G63" t="str">
         <f t="shared" si="0"/>
-        <v>T9V2A23</v>
-      </c>
-      <c r="H63" t="s">
-        <v>144</v>
-      </c>
-      <c r="I63" t="s">
-        <v>49</v>
-      </c>
-      <c r="J63" t="s">
-        <v>49</v>
+        <v/>
       </c>
       <c r="K63" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I63,"|",J63),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
-      </c>
-      <c r="L63">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A64,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
-      </c>
-      <c r="C64">
-        <v>24</v>
+        <v/>
       </c>
       <c r="D64" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C64,Assets!A:C,2,FALSE),"")</f>
-        <v>People</v>
+        <v/>
       </c>
       <c r="E64" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C64,Assets!A:C,3,FALSE),"")</f>
-        <v>Management</v>
-      </c>
-      <c r="F64">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G64" t="str">
         <f t="shared" si="0"/>
-        <v>T1V1A24</v>
-      </c>
-      <c r="H64" t="s">
-        <v>146</v>
-      </c>
-      <c r="I64" t="s">
-        <v>49</v>
-      </c>
-      <c r="J64" t="s">
-        <v>50</v>
+        <v/>
       </c>
       <c r="K64" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I64,"|",J64),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Low</v>
-      </c>
-      <c r="L64">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>3</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A65,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Information extortion</v>
-      </c>
-      <c r="C65">
-        <v>24</v>
+        <v/>
       </c>
       <c r="D65" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C65,Assets!A:C,2,FALSE),"")</f>
-        <v>People</v>
+        <v/>
       </c>
       <c r="E65" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C65,Assets!A:C,3,FALSE),"")</f>
-        <v>Management</v>
-      </c>
-      <c r="F65">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G65" t="str">
         <f t="shared" si="0"/>
-        <v>T3V2A24</v>
-      </c>
-      <c r="H65" t="s">
-        <v>147</v>
-      </c>
-      <c r="I65" t="s">
-        <v>48</v>
-      </c>
-      <c r="J65" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K65" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I65,"|",J65),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Very High</v>
-      </c>
-      <c r="L65">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A66,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
-      </c>
-      <c r="C66">
-        <v>25</v>
+        <v/>
       </c>
       <c r="D66" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C66,Assets!A:C,2,FALSE),"")</f>
-        <v>People</v>
+        <v/>
       </c>
       <c r="E66" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C66,Assets!A:C,3,FALSE),"")</f>
-        <v xml:space="preserve">Staff </v>
-      </c>
-      <c r="F66">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G66" t="str">
         <f t="shared" si="0"/>
-        <v>T1V1A25</v>
-      </c>
-      <c r="H66" t="s">
-        <v>148</v>
-      </c>
-      <c r="I66" t="s">
-        <v>48</v>
-      </c>
-      <c r="J66" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K66" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I66,"|",J66),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Very High</v>
-      </c>
-      <c r="L66">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>5</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A67,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Theft</v>
-      </c>
-      <c r="C67">
-        <v>25</v>
+        <v/>
       </c>
       <c r="D67" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C67,Assets!A:C,2,FALSE),"")</f>
-        <v>People</v>
+        <v/>
       </c>
       <c r="E67" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C67,Assets!A:C,3,FALSE),"")</f>
-        <v xml:space="preserve">Staff </v>
-      </c>
-      <c r="F67">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G67" t="str">
         <f t="shared" si="0"/>
-        <v>T5V2A25</v>
-      </c>
-      <c r="H67" t="s">
-        <v>149</v>
-      </c>
-      <c r="I67" t="s">
-        <v>50</v>
-      </c>
-      <c r="J67" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K67" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I67,"|",J67),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
-      </c>
-      <c r="L67">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>2</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B68" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A68,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Software attacks</v>
-      </c>
-      <c r="C68">
-        <v>26</v>
+        <v/>
       </c>
       <c r="D68" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C68,Assets!A:C,2,FALSE),"")</f>
-        <v>People</v>
+        <v/>
       </c>
       <c r="E68" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C68,Assets!A:C,3,FALSE),"")</f>
-        <v>Customers</v>
-      </c>
-      <c r="F68">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G68" t="str">
         <f t="shared" si="0"/>
-        <v>T2V1A26</v>
-      </c>
-      <c r="H68" t="s">
-        <v>150</v>
-      </c>
-      <c r="I68" t="s">
-        <v>48</v>
-      </c>
-      <c r="J68" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K68" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I68,"|",J68),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Very High</v>
-      </c>
-      <c r="L68">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>3</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A69,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Information extortion</v>
-      </c>
-      <c r="C69">
-        <v>26</v>
+        <v/>
       </c>
       <c r="D69" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C69,Assets!A:C,2,FALSE),"")</f>
-        <v>People</v>
+        <v/>
       </c>
       <c r="E69" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C69,Assets!A:C,3,FALSE),"")</f>
-        <v>Customers</v>
-      </c>
-      <c r="F69">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G69" t="str">
         <f t="shared" si="0"/>
-        <v>T3V2A26</v>
-      </c>
-      <c r="H69" t="s">
-        <v>151</v>
-      </c>
-      <c r="I69" t="s">
-        <v>50</v>
-      </c>
-      <c r="J69" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K69" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I69,"|",J69),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
-      </c>
-      <c r="L69">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A70,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
-      </c>
-      <c r="C70">
-        <v>27</v>
+        <v/>
       </c>
       <c r="D70" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C70,Assets!A:C,2,FALSE),"")</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="E70" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C70,Assets!A:C,3,FALSE),"")</f>
-        <v>Network design and configuration processes</v>
-      </c>
-      <c r="F70">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G70" t="str">
         <f t="shared" si="0"/>
-        <v>T1V1A27</v>
-      </c>
-      <c r="H70" t="s">
-        <v>152</v>
-      </c>
-      <c r="I70" t="s">
-        <v>49</v>
-      </c>
-      <c r="J70" t="s">
-        <v>48</v>
+        <v/>
       </c>
       <c r="K70" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I70,"|",J70),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
-      </c>
-      <c r="L70">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>6</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A71,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Technological obsolescence</v>
-      </c>
-      <c r="C71">
-        <v>27</v>
+        <v/>
       </c>
       <c r="D71" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C71,Assets!A:C,2,FALSE),"")</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="E71" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C71,Assets!A:C,3,FALSE),"")</f>
-        <v>Network design and configuration processes</v>
-      </c>
-      <c r="F71">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G71" t="str">
         <f t="shared" si="0"/>
-        <v>T6V2A27</v>
-      </c>
-      <c r="H71" t="s">
-        <v>153</v>
-      </c>
-      <c r="I71" t="s">
-        <v>49</v>
-      </c>
-      <c r="J71" t="s">
-        <v>50</v>
+        <v/>
       </c>
       <c r="K71" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I71,"|",J71),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Low</v>
-      </c>
-      <c r="L71">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B72" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A72,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
-      </c>
-      <c r="C72">
-        <v>28</v>
+        <v/>
       </c>
       <c r="D72" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C72,Assets!A:C,2,FALSE),"")</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="E72" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C72,Assets!A:C,3,FALSE),"")</f>
-        <v>Access control and identity management processes</v>
-      </c>
-      <c r="F72">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G72" t="str">
         <f t="shared" si="0"/>
-        <v>T1V1A28</v>
-      </c>
-      <c r="H72" t="s">
-        <v>154</v>
-      </c>
-      <c r="I72" t="s">
-        <v>50</v>
-      </c>
-      <c r="J72" t="s">
-        <v>51</v>
+        <v/>
       </c>
       <c r="K72" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I72,"|",J72),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Very Low</v>
-      </c>
-      <c r="L72">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>4</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A73,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Espionage and trespass</v>
-      </c>
-      <c r="C73">
-        <v>28</v>
+        <v/>
       </c>
       <c r="D73" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C73,Assets!A:C,2,FALSE),"")</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="E73" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C73,Assets!A:C,3,FALSE),"")</f>
-        <v>Access control and identity management processes</v>
-      </c>
-      <c r="F73">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G73" t="str">
         <f t="shared" si="0"/>
-        <v>T4V2A28</v>
-      </c>
-      <c r="H73" t="s">
-        <v>155</v>
-      </c>
-      <c r="I73" t="s">
-        <v>49</v>
-      </c>
-      <c r="J73" t="s">
-        <v>48</v>
+        <v/>
       </c>
       <c r="K73" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I73,"|",J73),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
-      </c>
-      <c r="L73">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>9</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A74,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Technical software failures or errors</v>
-      </c>
-      <c r="C74">
-        <v>29</v>
+        <v/>
       </c>
       <c r="D74" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C74,Assets!A:C,2,FALSE),"")</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="E74" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C74,Assets!A:C,3,FALSE),"")</f>
-        <v>Data backup and disaster recovery procedures</v>
-      </c>
-      <c r="F74">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G74" t="str">
         <f t="shared" si="0"/>
-        <v>T9V1A29</v>
-      </c>
-      <c r="H74" t="s">
-        <v>156</v>
-      </c>
-      <c r="I74" t="s">
-        <v>50</v>
-      </c>
-      <c r="J74" t="s">
-        <v>49</v>
+        <v/>
       </c>
       <c r="K74" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I74,"|",J74),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Low</v>
-      </c>
-      <c r="L74">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B75" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A75,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
-      </c>
-      <c r="C75">
-        <v>29</v>
+        <v/>
       </c>
       <c r="D75" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C75,Assets!A:C,2,FALSE),"")</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="E75" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C75,Assets!A:C,3,FALSE),"")</f>
-        <v>Data backup and disaster recovery procedures</v>
-      </c>
-      <c r="F75">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G75" t="str">
         <f t="shared" si="0"/>
-        <v>T1V2A29</v>
-      </c>
-      <c r="H75" t="s">
-        <v>157</v>
-      </c>
-      <c r="I75" t="s">
-        <v>49</v>
-      </c>
-      <c r="J75" t="s">
-        <v>48</v>
+        <v/>
       </c>
       <c r="K75" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I75,"|",J75),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
-      </c>
-      <c r="L75">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>7</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B76" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A76,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Forces of nature</v>
-      </c>
-      <c r="C76">
-        <v>29</v>
+        <v/>
       </c>
       <c r="D76" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C76,Assets!A:C,2,FALSE),"")</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="E76" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C76,Assets!A:C,3,FALSE),"")</f>
-        <v>Data backup and disaster recovery procedures</v>
-      </c>
-      <c r="F76">
-        <v>3</v>
+        <v/>
       </c>
       <c r="G76" t="str">
         <f t="shared" si="0"/>
-        <v>T7V3A29</v>
-      </c>
-      <c r="H76" t="s">
-        <v>158</v>
-      </c>
-      <c r="I76" t="s">
-        <v>51</v>
-      </c>
-      <c r="J76" t="s">
-        <v>49</v>
+        <v/>
       </c>
       <c r="K76" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I76,"|",J76),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Very Low</v>
-      </c>
-      <c r="L76">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B77" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A77,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
-      </c>
-      <c r="C77">
-        <v>30</v>
+        <v/>
       </c>
       <c r="D77" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C77,Assets!A:C,2,FALSE),"")</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="E77" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C77,Assets!A:C,3,FALSE),"")</f>
-        <v>Onboarding and offboarding procedures for staff</v>
-      </c>
-      <c r="F77">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G77" t="str">
         <f t="shared" si="0"/>
-        <v>T1V1A30</v>
-      </c>
-      <c r="H77" t="s">
-        <v>161</v>
-      </c>
-      <c r="I77" t="s">
-        <v>50</v>
-      </c>
-      <c r="J77" t="s">
-        <v>51</v>
+        <v/>
       </c>
       <c r="K77" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I77,"|",J77),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Very Low</v>
-      </c>
-      <c r="L77">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B78" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A78,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
-      </c>
-      <c r="C78">
-        <v>30</v>
+        <v/>
       </c>
       <c r="D78" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C78,Assets!A:C,2,FALSE),"")</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="E78" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C78,Assets!A:C,3,FALSE),"")</f>
-        <v>Onboarding and offboarding procedures for staff</v>
-      </c>
-      <c r="F78">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G78" t="str">
         <f t="shared" si="0"/>
-        <v>T1V2A30</v>
-      </c>
-      <c r="H78" t="s">
-        <v>162</v>
-      </c>
-      <c r="I78" t="s">
-        <v>49</v>
-      </c>
-      <c r="J78" t="s">
-        <v>51</v>
+        <v/>
       </c>
       <c r="K78" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I78,"|",J78),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Very Low</v>
-      </c>
-      <c r="L78">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A79,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
-      </c>
-      <c r="C79">
-        <v>31</v>
+        <v/>
       </c>
       <c r="D79" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C79,Assets!A:C,2,FALSE),"")</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="E79" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C79,Assets!A:C,3,FALSE),"")</f>
-        <v>Onboarding and offboarding procedures for customers</v>
-      </c>
-      <c r="F79">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G79" t="str">
         <f t="shared" si="0"/>
-        <v>T1V1A31</v>
-      </c>
-      <c r="H79" t="s">
-        <v>159</v>
-      </c>
-      <c r="I79" t="s">
-        <v>50</v>
-      </c>
-      <c r="J79" t="s">
-        <v>50</v>
+        <v/>
       </c>
       <c r="K79" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I79,"|",J79),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Low</v>
-      </c>
-      <c r="L79">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>4</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A80,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Espionage and trespass</v>
-      </c>
-      <c r="C80">
-        <v>31</v>
+        <v/>
       </c>
       <c r="D80" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C80,Assets!A:C,2,FALSE),"")</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="E80" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C80,Assets!A:C,3,FALSE),"")</f>
-        <v>Onboarding and offboarding procedures for customers</v>
-      </c>
-      <c r="F80">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G80" t="str">
         <f t="shared" si="0"/>
-        <v>T4V2A31</v>
-      </c>
-      <c r="H80" t="s">
-        <v>160</v>
-      </c>
-      <c r="I80" t="s">
-        <v>48</v>
-      </c>
-      <c r="J80" t="s">
-        <v>48</v>
+        <v/>
       </c>
       <c r="K80" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I80,"|",J80),RiskValues!C:D,2,FALSE),"")</f>
-        <v>High</v>
-      </c>
-      <c r="L80">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A81,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
-      </c>
-      <c r="C81">
-        <v>32</v>
+        <v/>
       </c>
       <c r="D81" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C81,Assets!A:C,2,FALSE),"")</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="E81" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C81,Assets!A:C,3,FALSE),"")</f>
-        <v>Risk management and business continuity planning</v>
-      </c>
-      <c r="F81">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G81" t="str">
         <f t="shared" si="0"/>
-        <v>T1V1A32</v>
-      </c>
-      <c r="H81" t="s">
-        <v>163</v>
-      </c>
-      <c r="I81" t="s">
-        <v>49</v>
-      </c>
-      <c r="J81" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K81" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I81,"|",J81),RiskValues!C:D,2,FALSE),"")</f>
-        <v>High</v>
-      </c>
-      <c r="L81">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>7</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A82,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Forces of nature</v>
-      </c>
-      <c r="C82">
-        <v>32</v>
+        <v/>
       </c>
       <c r="D82" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C82,Assets!A:C,2,FALSE),"")</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="E82" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C82,Assets!A:C,3,FALSE),"")</f>
-        <v>Risk management and business continuity planning</v>
-      </c>
-      <c r="F82">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G82" t="str">
         <f t="shared" si="0"/>
-        <v>T7V2A32</v>
-      </c>
-      <c r="H82" t="s">
-        <v>164</v>
-      </c>
-      <c r="I82" t="s">
-        <v>49</v>
-      </c>
-      <c r="J82" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K82" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I82,"|",J82),RiskValues!C:D,2,FALSE),"")</f>
-        <v>High</v>
-      </c>
-      <c r="L82">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A83,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
-      </c>
-      <c r="C83">
-        <v>33</v>
+        <v/>
       </c>
       <c r="D83" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C83,Assets!A:C,2,FALSE),"")</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="E83" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C83,Assets!A:C,3,FALSE),"")</f>
-        <v>Physical security procedures (building and access control)</v>
-      </c>
-      <c r="F83">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G83" t="str">
         <f t="shared" si="0"/>
-        <v>T1V1A33</v>
-      </c>
-      <c r="H83" t="s">
-        <v>165</v>
-      </c>
-      <c r="I83" t="s">
-        <v>49</v>
-      </c>
-      <c r="J83" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K83" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I83,"|",J83),RiskValues!C:D,2,FALSE),"")</f>
-        <v>High</v>
-      </c>
-      <c r="L83">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>4</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A84,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Espionage and trespass</v>
-      </c>
-      <c r="C84">
-        <v>33</v>
+        <v/>
       </c>
       <c r="D84" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C84,Assets!A:C,2,FALSE),"")</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="E84" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C84,Assets!A:C,3,FALSE),"")</f>
-        <v>Physical security procedures (building and access control)</v>
-      </c>
-      <c r="F84">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G84" t="str">
         <f t="shared" si="0"/>
-        <v>T4V2A33</v>
-      </c>
-      <c r="H84" t="s">
-        <v>166</v>
-      </c>
-      <c r="I84" t="s">
-        <v>48</v>
-      </c>
-      <c r="J84" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K84" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I84,"|",J84),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Very High</v>
-      </c>
-      <c r="L84">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B85" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A85,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>People errors</v>
-      </c>
-      <c r="C85">
-        <v>34</v>
+        <v/>
       </c>
       <c r="D85" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C85,Assets!A:C,2,FALSE),"")</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="E85" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C85,Assets!A:C,3,FALSE),"")</f>
-        <v>IT service management and support workflows</v>
-      </c>
-      <c r="F85">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G85" t="str">
         <f t="shared" si="0"/>
-        <v>T1V1A34</v>
-      </c>
-      <c r="H85" t="s">
-        <v>167</v>
-      </c>
-      <c r="I85" t="s">
-        <v>49</v>
-      </c>
-      <c r="J85" t="s">
-        <v>48</v>
+        <v/>
       </c>
       <c r="K85" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I85,"|",J85),RiskValues!C:D,2,FALSE),"")</f>
-        <v>Moderate</v>
-      </c>
-      <c r="L85">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>4</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A86,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v>Espionage and trespass</v>
-      </c>
-      <c r="C86">
-        <v>34</v>
+        <v/>
       </c>
       <c r="D86" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C86,Assets!A:C,2,FALSE),"")</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="E86" t="str">
         <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C86,Assets!A:C,3,FALSE),"")</f>
-        <v>IT service management and support workflows</v>
-      </c>
-      <c r="F86">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G86" t="str">
         <f t="shared" si="0"/>
-        <v>T4V2A34</v>
-      </c>
-      <c r="H86" t="s">
-        <v>168</v>
-      </c>
-      <c r="I86" t="s">
-        <v>49</v>
-      </c>
-      <c r="J86" t="s">
-        <v>47</v>
+        <v/>
       </c>
       <c r="K86" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I86,"|",J86),RiskValues!C:D,2,FALSE),"")</f>
-        <v>High</v>
-      </c>
-      <c r="L86">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B87" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A87,InfoSecThreats!A:B,2,FALSE),"")</f>
         <v/>
@@ -5615,7 +4241,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B88" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A88,InfoSecThreats!A:B,2,FALSE),"")</f>
         <v/>
@@ -5637,7 +4263,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B89" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A89,InfoSecThreats!A:B,2,FALSE),"")</f>
         <v/>
@@ -5659,7 +4285,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B90" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A90,InfoSecThreats!A:B,2,FALSE),"")</f>
         <v/>
@@ -5681,7 +4307,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B91" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A91,InfoSecThreats!A:B,2,FALSE),"")</f>
         <v/>
@@ -5703,7 +4329,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A92,InfoSecThreats!A:B,2,FALSE),"")</f>
         <v/>
@@ -5725,7 +4351,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B93" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A93,InfoSecThreats!A:B,2,FALSE),"")</f>
         <v/>
@@ -5747,7 +4373,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B94" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A94,InfoSecThreats!A:B,2,FALSE),"")</f>
         <v/>
@@ -5769,7 +4395,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B95" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A95,InfoSecThreats!A:B,2,FALSE),"")</f>
         <v/>
@@ -5791,7 +4417,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B96" t="str">
         <f>_xlfn.IFNA(VLOOKUP(A96,InfoSecThreats!A:B,2,FALSE),"")</f>
         <v/>
@@ -6091,7 +4717,7 @@
         <v/>
       </c>
       <c r="G109" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G109:G172" si="1">IF(ISBLANK(F109),"",_xlfn.CONCAT("T",A109,"V",F109,"A",C109))</f>
         <v/>
       </c>
       <c r="K109" t="str">
@@ -6113,7 +4739,7 @@
         <v/>
       </c>
       <c r="G110" t="str">
-        <f t="shared" ref="G110:G173" si="1">IF(ISBLANK(F110),"",_xlfn.CONCAT("T",A110,"V",F110,"A",C110))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K110" t="str">
@@ -7499,7 +6125,7 @@
         <v/>
       </c>
       <c r="G173" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="G173:G236" si="2">IF(ISBLANK(F173),"",_xlfn.CONCAT("T",A173,"V",F173,"A",C173))</f>
         <v/>
       </c>
       <c r="K173" t="str">
@@ -7521,7 +6147,7 @@
         <v/>
       </c>
       <c r="G174" t="str">
-        <f t="shared" ref="G174:G237" si="2">IF(ISBLANK(F174),"",_xlfn.CONCAT("T",A174,"V",F174,"A",C174))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K174" t="str">
@@ -8907,7 +7533,7 @@
         <v/>
       </c>
       <c r="G237" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="G237:G300" si="3">IF(ISBLANK(F237),"",_xlfn.CONCAT("T",A237,"V",F237,"A",C237))</f>
         <v/>
       </c>
       <c r="K237" t="str">
@@ -8929,7 +7555,7 @@
         <v/>
       </c>
       <c r="G238" t="str">
-        <f t="shared" ref="G238:G301" si="3">IF(ISBLANK(F238),"",_xlfn.CONCAT("T",A238,"V",F238,"A",C238))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K238" t="str">
@@ -10315,7 +8941,7 @@
         <v/>
       </c>
       <c r="G301" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="G301:G364" si="4">IF(ISBLANK(F301),"",_xlfn.CONCAT("T",A301,"V",F301,"A",C301))</f>
         <v/>
       </c>
       <c r="K301" t="str">
@@ -10337,7 +8963,7 @@
         <v/>
       </c>
       <c r="G302" t="str">
-        <f t="shared" ref="G302:G365" si="4">IF(ISBLANK(F302),"",_xlfn.CONCAT("T",A302,"V",F302,"A",C302))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K302" t="str">
@@ -11723,7 +10349,7 @@
         <v/>
       </c>
       <c r="G365" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="G365:G428" si="5">IF(ISBLANK(F365),"",_xlfn.CONCAT("T",A365,"V",F365,"A",C365))</f>
         <v/>
       </c>
       <c r="K365" t="str">
@@ -11745,7 +10371,7 @@
         <v/>
       </c>
       <c r="G366" t="str">
-        <f t="shared" ref="G366:G429" si="5">IF(ISBLANK(F366),"",_xlfn.CONCAT("T",A366,"V",F366,"A",C366))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K366" t="str">
@@ -13131,7 +11757,7 @@
         <v/>
       </c>
       <c r="G429" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="G429:G443" si="6">IF(ISBLANK(F429),"",_xlfn.CONCAT("T",A429,"V",F429,"A",C429))</f>
         <v/>
       </c>
       <c r="K429" t="str">
@@ -13153,7 +11779,7 @@
         <v/>
       </c>
       <c r="G430" t="str">
-        <f t="shared" ref="G430:G444" si="6">IF(ISBLANK(F430),"",_xlfn.CONCAT("T",A430,"V",F430,"A",C430))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K430" t="str">
@@ -13447,30 +12073,8 @@
         <v/>
       </c>
     </row>
-    <row r="444" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B444" t="str">
-        <f>_xlfn.IFNA(VLOOKUP(A444,InfoSecThreats!A:B,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="D444" t="str">
-        <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C444,Assets!A:C,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E444" t="str">
-        <f>_xlfn.IFNA(VLOOKUP(Vulnerabilities!C444,Assets!A:C,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G444" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="K444" t="str">
-        <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT(I444,"|",J444),RiskValues!C:D,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L444" xr:uid="{40C2DAE8-51BF-4509-BC4F-A78D257FBFC8}"/>
+  <autoFilter ref="A1:L443" xr:uid="{40C2DAE8-51BF-4509-BC4F-A78D257FBFC8}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
@@ -13480,7 +12084,7 @@
           <x14:formula1>
             <xm:f>RiskValues!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:J444</xm:sqref>
+          <xm:sqref>I2:J443</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -13495,7 +12099,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -13505,20 +12109,20 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -13648,11 +12252,11 @@
       </c>
       <c r="B3" t="str">
         <f>IF(VLOOKUP($A3,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A3,Assets!$A:$C,2,FALSE))</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="C3" t="str">
         <f>IF(VLOOKUP($A3,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A3,Assets!$A:$C,3,FALSE))</f>
-        <v>Bank Account</v>
+        <v>PCs</v>
       </c>
       <c r="D3" s="12">
         <v>1</v>
@@ -13663,7 +12267,7 @@
       </c>
       <c r="F3" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D3,"A",$A3),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T2V1A1</v>
+        <v/>
       </c>
       <c r="G3" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D3,"A",$A3),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -13712,11 +12316,11 @@
       </c>
       <c r="B4" t="str">
         <f>IF(VLOOKUP($A4,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A4,Assets!$A:$C,2,FALSE))</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="C4" t="str">
         <f>IF(VLOOKUP($A4,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A4,Assets!$A:$C,3,FALSE))</f>
-        <v>Bank Account</v>
+        <v>PCs</v>
       </c>
       <c r="D4" s="12">
         <v>2</v>
@@ -13776,11 +12380,11 @@
       </c>
       <c r="B5" t="str">
         <f>IF(VLOOKUP($A5,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A5,Assets!$A:$C,2,FALSE))</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="C5" t="str">
         <f>IF(VLOOKUP($A5,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A5,Assets!$A:$C,3,FALSE))</f>
-        <v>Bank Account</v>
+        <v>PCs</v>
       </c>
       <c r="D5" s="12">
         <v>3</v>
@@ -13795,7 +12399,7 @@
       </c>
       <c r="G5" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D5,"A",$A5),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T3V3A1</v>
       </c>
       <c r="H5" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",H$1,"V",$D5,"A",$A5),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -13840,11 +12444,11 @@
       </c>
       <c r="B6" s="8" t="str">
         <f>IF(VLOOKUP($A6,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A6,Assets!$A:$C,2,FALSE))</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="C6" s="8" t="str">
         <f>IF(VLOOKUP($A6,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A6,Assets!$A:$C,3,FALSE))</f>
-        <v>Bank Account</v>
+        <v>PCs</v>
       </c>
       <c r="D6" s="13">
         <v>4</v>
@@ -13905,18 +12509,18 @@
       </c>
       <c r="B7" t="str">
         <f>IF(VLOOKUP($A7,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A7,Assets!$A:$C,2,FALSE))</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="C7" t="str">
         <f>IF(VLOOKUP($A7,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A7,Assets!$A:$C,3,FALSE))</f>
-        <v>Customer Data</v>
+        <v>Router</v>
       </c>
       <c r="D7" s="12">
         <v>1</v>
       </c>
       <c r="E7" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D7,"A",$A7),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V1A2</v>
+        <v/>
       </c>
       <c r="F7" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D7,"A",$A7),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -13948,7 +12552,7 @@
       </c>
       <c r="M7" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",M$1,"V",$D7,"A",$A7),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T9V1A2</v>
       </c>
       <c r="N7" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",N$1,"V",$D7,"A",$A7),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -13970,11 +12574,11 @@
       </c>
       <c r="B8" t="str">
         <f>IF(VLOOKUP($A8,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A8,Assets!$A:$C,2,FALSE))</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="C8" t="str">
         <f>IF(VLOOKUP($A8,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A8,Assets!$A:$C,3,FALSE))</f>
-        <v>Customer Data</v>
+        <v>Router</v>
       </c>
       <c r="D8" s="12">
         <v>2</v>
@@ -13993,11 +12597,11 @@
       </c>
       <c r="H8" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",H$1,"V",$D8,"A",$A8),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T4V2A2</v>
       </c>
       <c r="I8" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D8,"A",$A8),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T5V2A2</v>
+        <v/>
       </c>
       <c r="J8" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",J$1,"V",$D8,"A",$A8),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -14035,11 +12639,11 @@
       </c>
       <c r="B9" t="str">
         <f>IF(VLOOKUP($A9,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A9,Assets!$A:$C,2,FALSE))</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="C9" t="str">
         <f>IF(VLOOKUP($A9,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A9,Assets!$A:$C,3,FALSE))</f>
-        <v>Customer Data</v>
+        <v>Router</v>
       </c>
       <c r="D9" s="12">
         <v>3</v>
@@ -14062,7 +12666,7 @@
       </c>
       <c r="I9" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D9,"A",$A9),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T5V3A2</v>
       </c>
       <c r="J9" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",J$1,"V",$D9,"A",$A9),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -14074,7 +12678,7 @@
       </c>
       <c r="L9" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",L$1,"V",$D9,"A",$A9),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T8V3A2</v>
+        <v/>
       </c>
       <c r="M9" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",M$1,"V",$D9,"A",$A9),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -14100,11 +12704,11 @@
       </c>
       <c r="B10" s="8" t="str">
         <f>IF(VLOOKUP($A10,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A10,Assets!$A:$C,2,FALSE))</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="C10" s="8" t="str">
         <f>IF(VLOOKUP($A10,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A10,Assets!$A:$C,3,FALSE))</f>
-        <v>Customer Data</v>
+        <v>Router</v>
       </c>
       <c r="D10" s="13">
         <v>4</v>
@@ -14135,7 +12739,7 @@
       </c>
       <c r="K10" s="17" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",K$1,"V",$D10,"A",$A10),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T7V4A2</v>
+        <v/>
       </c>
       <c r="L10" s="17" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",L$1,"V",$D10,"A",$A10),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -14165,18 +12769,18 @@
       </c>
       <c r="B11" t="str">
         <f>IF(VLOOKUP($A11,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A11,Assets!$A:$C,2,FALSE))</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="C11" t="str">
         <f>IF(VLOOKUP($A11,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A11,Assets!$A:$C,3,FALSE))</f>
-        <v>Employee data (HR records, payroll, personal information)</v>
+        <v>Switch</v>
       </c>
       <c r="D11" s="12">
         <v>1</v>
       </c>
       <c r="E11" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D11,"A",$A11),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V1A3</v>
+        <v/>
       </c>
       <c r="F11" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D11,"A",$A11),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -14204,7 +12808,7 @@
       </c>
       <c r="L11" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",L$1,"V",$D11,"A",$A11),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T8V1A3</v>
       </c>
       <c r="M11" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",M$1,"V",$D11,"A",$A11),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -14230,11 +12834,11 @@
       </c>
       <c r="B12" t="str">
         <f>IF(VLOOKUP($A12,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A12,Assets!$A:$C,2,FALSE))</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="C12" t="str">
         <f>IF(VLOOKUP($A12,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A12,Assets!$A:$C,3,FALSE))</f>
-        <v>Employee data (HR records, payroll, personal information)</v>
+        <v>Switch</v>
       </c>
       <c r="D12" s="12">
         <v>2</v>
@@ -14245,7 +12849,7 @@
       </c>
       <c r="F12" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D12,"A",$A12),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T2V2A3</v>
+        <v/>
       </c>
       <c r="G12" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D12,"A",$A12),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -14253,7 +12857,7 @@
       </c>
       <c r="H12" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",H$1,"V",$D12,"A",$A12),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T4V2A3</v>
       </c>
       <c r="I12" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D12,"A",$A12),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -14295,11 +12899,11 @@
       </c>
       <c r="B13" t="str">
         <f>IF(VLOOKUP($A13,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A13,Assets!$A:$C,2,FALSE))</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="C13" t="str">
         <f>IF(VLOOKUP($A13,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A13,Assets!$A:$C,3,FALSE))</f>
-        <v>Employee data (HR records, payroll, personal information)</v>
+        <v>Switch</v>
       </c>
       <c r="D13" s="12">
         <v>3</v>
@@ -14322,7 +12926,7 @@
       </c>
       <c r="I13" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D13,"A",$A13),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T5V3A3</v>
+        <v/>
       </c>
       <c r="J13" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",J$1,"V",$D13,"A",$A13),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -14346,7 +12950,7 @@
       </c>
       <c r="O13" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",O$1,"V",$D13,"A",$A13),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T11V3A3</v>
       </c>
       <c r="P13" s="12" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",P$1,"V",$D13,"A",$A13),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -14360,11 +12964,11 @@
       </c>
       <c r="B14" s="8" t="str">
         <f>IF(VLOOKUP($A14,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A14,Assets!$A:$C,2,FALSE))</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="C14" s="8" t="str">
         <f>IF(VLOOKUP($A14,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A14,Assets!$A:$C,3,FALSE))</f>
-        <v>Employee data (HR records, payroll, personal information)</v>
+        <v>Switch</v>
       </c>
       <c r="D14" s="13">
         <v>4</v>
@@ -14403,7 +13007,7 @@
       </c>
       <c r="M14" s="17" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",M$1,"V",$D14,"A",$A14),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T9V4A3</v>
+        <v/>
       </c>
       <c r="N14" s="17" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",N$1,"V",$D14,"A",$A14),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -14425,22 +13029,22 @@
       </c>
       <c r="B15" t="str">
         <f>IF(VLOOKUP($A15,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A15,Assets!$A:$C,2,FALSE))</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="C15" t="str">
         <f>IF(VLOOKUP($A15,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A15,Assets!$A:$C,3,FALSE))</f>
-        <v>CRM</v>
+        <v>Server / VM Host</v>
       </c>
       <c r="D15" s="12">
         <v>1</v>
       </c>
       <c r="E15" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D15,"A",$A15),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V1A4</v>
+        <v/>
       </c>
       <c r="F15" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D15,"A",$A15),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T2V1A4</v>
       </c>
       <c r="G15" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D15,"A",$A15),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -14490,22 +13094,22 @@
       </c>
       <c r="B16" t="str">
         <f>IF(VLOOKUP($A16,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A16,Assets!$A:$C,2,FALSE))</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="C16" t="str">
         <f>IF(VLOOKUP($A16,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A16,Assets!$A:$C,3,FALSE))</f>
-        <v>CRM</v>
+        <v>Server / VM Host</v>
       </c>
       <c r="D16" s="12">
         <v>2</v>
       </c>
       <c r="E16" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D16,"A",$A16),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T1V2A4</v>
       </c>
       <c r="F16" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D16,"A",$A16),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T2V2A4</v>
+        <v/>
       </c>
       <c r="G16" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D16,"A",$A16),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -14555,11 +13159,11 @@
       </c>
       <c r="B17" t="str">
         <f>IF(VLOOKUP($A17,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A17,Assets!$A:$C,2,FALSE))</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="C17" t="str">
         <f>IF(VLOOKUP($A17,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A17,Assets!$A:$C,3,FALSE))</f>
-        <v>CRM</v>
+        <v>Server / VM Host</v>
       </c>
       <c r="D17" s="12">
         <v>3</v>
@@ -14598,7 +13202,7 @@
       </c>
       <c r="M17" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",M$1,"V",$D17,"A",$A17),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T9V3A4</v>
+        <v/>
       </c>
       <c r="N17" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",N$1,"V",$D17,"A",$A17),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -14620,11 +13224,11 @@
       </c>
       <c r="B18" s="8" t="str">
         <f>IF(VLOOKUP($A18,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A18,Assets!$A:$C,2,FALSE))</f>
-        <v>Data</v>
+        <v>Hardware</v>
       </c>
       <c r="C18" s="8" t="str">
         <f>IF(VLOOKUP($A18,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A18,Assets!$A:$C,3,FALSE))</f>
-        <v>CRM</v>
+        <v>Server / VM Host</v>
       </c>
       <c r="D18" s="13">
         <v>4</v>
@@ -14675,7 +13279,7 @@
       </c>
       <c r="P18" s="13" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",P$1,"V",$D18,"A",$A18),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T12V4A4</v>
+        <v/>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -14685,18 +13289,18 @@
       </c>
       <c r="B19" t="str">
         <f>IF(VLOOKUP($A19,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A19,Assets!$A:$C,2,FALSE))</f>
-        <v>Data</v>
+        <v>Software</v>
       </c>
       <c r="C19" t="str">
         <f>IF(VLOOKUP($A19,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A19,Assets!$A:$C,3,FALSE))</f>
-        <v>Financial data (accounting records, invoices, tax data)</v>
+        <v>OpenWRT</v>
       </c>
       <c r="D19" s="12">
         <v>1</v>
       </c>
       <c r="E19" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D19,"A",$A19),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V1A5</v>
+        <v/>
       </c>
       <c r="F19" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D19,"A",$A19),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -14716,7 +13320,7 @@
       </c>
       <c r="J19" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",J$1,"V",$D19,"A",$A19),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T6V1A5</v>
       </c>
       <c r="K19" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",K$1,"V",$D19,"A",$A19),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -14750,11 +13354,11 @@
       </c>
       <c r="B20" t="str">
         <f>IF(VLOOKUP($A20,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A20,Assets!$A:$C,2,FALSE))</f>
-        <v>Data</v>
+        <v>Software</v>
       </c>
       <c r="C20" t="str">
         <f>IF(VLOOKUP($A20,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A20,Assets!$A:$C,3,FALSE))</f>
-        <v>Financial data (accounting records, invoices, tax data)</v>
+        <v>OpenWRT</v>
       </c>
       <c r="D20" s="12">
         <v>2</v>
@@ -14765,7 +13369,7 @@
       </c>
       <c r="F20" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D20,"A",$A20),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T2V2A5</v>
+        <v/>
       </c>
       <c r="G20" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D20,"A",$A20),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -14793,7 +13397,7 @@
       </c>
       <c r="M20" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",M$1,"V",$D20,"A",$A20),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T9V2A5</v>
       </c>
       <c r="N20" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",N$1,"V",$D20,"A",$A20),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -14815,11 +13419,11 @@
       </c>
       <c r="B21" t="str">
         <f>IF(VLOOKUP($A21,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A21,Assets!$A:$C,2,FALSE))</f>
-        <v>Data</v>
+        <v>Software</v>
       </c>
       <c r="C21" t="str">
         <f>IF(VLOOKUP($A21,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A21,Assets!$A:$C,3,FALSE))</f>
-        <v>Financial data (accounting records, invoices, tax data)</v>
+        <v>OpenWRT</v>
       </c>
       <c r="D21" s="12">
         <v>3</v>
@@ -14834,7 +13438,7 @@
       </c>
       <c r="G21" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D21,"A",$A21),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T3V3A5</v>
+        <v/>
       </c>
       <c r="H21" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",H$1,"V",$D21,"A",$A21),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -14880,11 +13484,11 @@
       </c>
       <c r="B22" s="8" t="str">
         <f>IF(VLOOKUP($A22,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A22,Assets!$A:$C,2,FALSE))</f>
-        <v>Data</v>
+        <v>Software</v>
       </c>
       <c r="C22" s="8" t="str">
         <f>IF(VLOOKUP($A22,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A22,Assets!$A:$C,3,FALSE))</f>
-        <v>Financial data (accounting records, invoices, tax data)</v>
+        <v>OpenWRT</v>
       </c>
       <c r="D22" s="13">
         <v>4</v>
@@ -14919,7 +13523,7 @@
       </c>
       <c r="L22" s="17" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",L$1,"V",$D22,"A",$A22),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T8V4A5</v>
+        <v/>
       </c>
       <c r="M22" s="17" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",M$1,"V",$D22,"A",$A22),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -14945,22 +13549,22 @@
       </c>
       <c r="B23" t="str">
         <f>IF(VLOOKUP($A23,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A23,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>Software</v>
       </c>
       <c r="C23" t="str">
         <f>IF(VLOOKUP($A23,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A23,Assets!$A:$C,3,FALSE))</f>
-        <v>Backup Data</v>
+        <v>LuCI</v>
       </c>
       <c r="D23" s="12">
         <v>1</v>
       </c>
       <c r="E23" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D23,"A",$A23),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V1A6</v>
+        <v/>
       </c>
       <c r="F23" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D23,"A",$A23),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T2V1A6</v>
       </c>
       <c r="G23" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D23,"A",$A23),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -15010,11 +13614,11 @@
       </c>
       <c r="B24" t="str">
         <f>IF(VLOOKUP($A24,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A24,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>Software</v>
       </c>
       <c r="C24" t="str">
         <f>IF(VLOOKUP($A24,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A24,Assets!$A:$C,3,FALSE))</f>
-        <v>Backup Data</v>
+        <v>LuCI</v>
       </c>
       <c r="D24" s="12">
         <v>2</v>
@@ -15037,7 +13641,7 @@
       </c>
       <c r="I24" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D24,"A",$A24),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T5V2A6</v>
+        <v/>
       </c>
       <c r="J24" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",J$1,"V",$D24,"A",$A24),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -15075,11 +13679,11 @@
       </c>
       <c r="B25" t="str">
         <f>IF(VLOOKUP($A25,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A25,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>Software</v>
       </c>
       <c r="C25" t="str">
         <f>IF(VLOOKUP($A25,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A25,Assets!$A:$C,3,FALSE))</f>
-        <v>Backup Data</v>
+        <v>LuCI</v>
       </c>
       <c r="D25" s="12">
         <v>3</v>
@@ -15094,7 +13698,7 @@
       </c>
       <c r="G25" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D25,"A",$A25),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T3V3A6</v>
+        <v/>
       </c>
       <c r="H25" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",H$1,"V",$D25,"A",$A25),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -15140,11 +13744,11 @@
       </c>
       <c r="B26" s="8" t="str">
         <f>IF(VLOOKUP($A26,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A26,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>Software</v>
       </c>
       <c r="C26" s="8" t="str">
         <f>IF(VLOOKUP($A26,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A26,Assets!$A:$C,3,FALSE))</f>
-        <v>Backup Data</v>
+        <v>LuCI</v>
       </c>
       <c r="D26" s="13">
         <v>4</v>
@@ -15175,7 +13779,7 @@
       </c>
       <c r="K26" s="17" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",K$1,"V",$D26,"A",$A26),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T7V4A6</v>
+        <v/>
       </c>
       <c r="L26" s="17" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",L$1,"V",$D26,"A",$A26),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -15205,22 +13809,22 @@
       </c>
       <c r="B27" t="str">
         <f>IF(VLOOKUP($A27,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A27,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>Software</v>
       </c>
       <c r="C27" t="str">
         <f>IF(VLOOKUP($A27,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A27,Assets!$A:$C,3,FALSE))</f>
-        <v>Routers and firewalls</v>
+        <v>Accounting Software</v>
       </c>
       <c r="D27" s="12">
         <v>1</v>
       </c>
       <c r="E27" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D27,"A",$A27),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V1A7</v>
+        <v/>
       </c>
       <c r="F27" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D27,"A",$A27),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T2V1A7</v>
       </c>
       <c r="G27" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D27,"A",$A27),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -15270,11 +13874,11 @@
       </c>
       <c r="B28" t="str">
         <f>IF(VLOOKUP($A28,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A28,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>Software</v>
       </c>
       <c r="C28" t="str">
         <f>IF(VLOOKUP($A28,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A28,Assets!$A:$C,3,FALSE))</f>
-        <v>Routers and firewalls</v>
+        <v>Accounting Software</v>
       </c>
       <c r="D28" s="12">
         <v>2</v>
@@ -15285,7 +13889,7 @@
       </c>
       <c r="F28" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D28,"A",$A28),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T2V2A7</v>
+        <v/>
       </c>
       <c r="G28" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D28,"A",$A28),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -15335,11 +13939,11 @@
       </c>
       <c r="B29" t="str">
         <f>IF(VLOOKUP($A29,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A29,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>Software</v>
       </c>
       <c r="C29" t="str">
         <f>IF(VLOOKUP($A29,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A29,Assets!$A:$C,3,FALSE))</f>
-        <v>Routers and firewalls</v>
+        <v>Accounting Software</v>
       </c>
       <c r="D29" s="12">
         <v>3</v>
@@ -15374,7 +13978,7 @@
       </c>
       <c r="L29" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",L$1,"V",$D29,"A",$A29),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T8V3A7</v>
+        <v/>
       </c>
       <c r="M29" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",M$1,"V",$D29,"A",$A29),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -15400,11 +14004,11 @@
       </c>
       <c r="B30" s="8" t="str">
         <f>IF(VLOOKUP($A30,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A30,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>Software</v>
       </c>
       <c r="C30" s="8" t="str">
         <f>IF(VLOOKUP($A30,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A30,Assets!$A:$C,3,FALSE))</f>
-        <v>Routers and firewalls</v>
+        <v>Accounting Software</v>
       </c>
       <c r="D30" s="13">
         <v>4</v>
@@ -15427,7 +14031,7 @@
       </c>
       <c r="I30" s="17" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D30,"A",$A30),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T5V4A7</v>
+        <v/>
       </c>
       <c r="J30" s="17" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",J$1,"V",$D30,"A",$A30),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -15465,22 +14069,22 @@
       </c>
       <c r="B31" t="str">
         <f>IF(VLOOKUP($A31,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A31,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>Software</v>
       </c>
       <c r="C31" t="str">
         <f>IF(VLOOKUP($A31,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A31,Assets!$A:$C,3,FALSE))</f>
-        <v>Switch</v>
+        <v xml:space="preserve">Dropbear SSH </v>
       </c>
       <c r="D31" s="12">
         <v>1</v>
       </c>
       <c r="E31" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D31,"A",$A31),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V1A8</v>
+        <v/>
       </c>
       <c r="F31" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D31,"A",$A31),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T2V1A8</v>
       </c>
       <c r="G31" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D31,"A",$A31),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -15530,11 +14134,11 @@
       </c>
       <c r="B32" t="str">
         <f>IF(VLOOKUP($A32,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A32,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>Software</v>
       </c>
       <c r="C32" t="str">
         <f>IF(VLOOKUP($A32,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A32,Assets!$A:$C,3,FALSE))</f>
-        <v>Switch</v>
+        <v xml:space="preserve">Dropbear SSH </v>
       </c>
       <c r="D32" s="12">
         <v>2</v>
@@ -15553,7 +14157,7 @@
       </c>
       <c r="H32" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",H$1,"V",$D32,"A",$A32),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T4V2A8</v>
+        <v/>
       </c>
       <c r="I32" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D32,"A",$A32),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -15595,11 +14199,11 @@
       </c>
       <c r="B33" t="str">
         <f>IF(VLOOKUP($A33,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A33,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>Software</v>
       </c>
       <c r="C33" t="str">
         <f>IF(VLOOKUP($A33,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A33,Assets!$A:$C,3,FALSE))</f>
-        <v>Switch</v>
+        <v xml:space="preserve">Dropbear SSH </v>
       </c>
       <c r="D33" s="12">
         <v>3</v>
@@ -15646,7 +14250,7 @@
       </c>
       <c r="O33" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",O$1,"V",$D33,"A",$A33),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T11V3A8</v>
+        <v/>
       </c>
       <c r="P33" s="12" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",P$1,"V",$D33,"A",$A33),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -15660,11 +14264,11 @@
       </c>
       <c r="B34" s="8" t="str">
         <f>IF(VLOOKUP($A34,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A34,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>Software</v>
       </c>
       <c r="C34" s="8" t="str">
         <f>IF(VLOOKUP($A34,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A34,Assets!$A:$C,3,FALSE))</f>
-        <v>Switch</v>
+        <v xml:space="preserve">Dropbear SSH </v>
       </c>
       <c r="D34" s="13">
         <v>4</v>
@@ -15725,18 +14329,18 @@
       </c>
       <c r="B35" t="str">
         <f>IF(VLOOKUP($A35,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A35,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>People</v>
       </c>
       <c r="C35" t="str">
         <f>IF(VLOOKUP($A35,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A35,Assets!$A:$C,3,FALSE))</f>
-        <v xml:space="preserve">Desktop computers and laptops </v>
+        <v>Manager</v>
       </c>
       <c r="D35" s="12">
         <v>1</v>
       </c>
       <c r="E35" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D35,"A",$A35),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T1V1A9</v>
       </c>
       <c r="F35" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D35,"A",$A35),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -15752,7 +14356,7 @@
       </c>
       <c r="I35" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D35,"A",$A35),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T5V1A9</v>
+        <v/>
       </c>
       <c r="J35" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",J$1,"V",$D35,"A",$A35),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -15790,11 +14394,11 @@
       </c>
       <c r="B36" t="str">
         <f>IF(VLOOKUP($A36,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A36,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>People</v>
       </c>
       <c r="C36" t="str">
         <f>IF(VLOOKUP($A36,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A36,Assets!$A:$C,3,FALSE))</f>
-        <v xml:space="preserve">Desktop computers and laptops </v>
+        <v>Manager</v>
       </c>
       <c r="D36" s="12">
         <v>2</v>
@@ -15805,7 +14409,7 @@
       </c>
       <c r="F36" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D36,"A",$A36),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T2V2A9</v>
+        <v/>
       </c>
       <c r="G36" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D36,"A",$A36),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -15855,11 +14459,11 @@
       </c>
       <c r="B37" t="str">
         <f>IF(VLOOKUP($A37,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A37,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>People</v>
       </c>
       <c r="C37" t="str">
         <f>IF(VLOOKUP($A37,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A37,Assets!$A:$C,3,FALSE))</f>
-        <v xml:space="preserve">Desktop computers and laptops </v>
+        <v>Manager</v>
       </c>
       <c r="D37" s="12">
         <v>3</v>
@@ -15920,11 +14524,11 @@
       </c>
       <c r="B38" s="8" t="str">
         <f>IF(VLOOKUP($A38,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A38,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>People</v>
       </c>
       <c r="C38" s="8" t="str">
         <f>IF(VLOOKUP($A38,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A38,Assets!$A:$C,3,FALSE))</f>
-        <v xml:space="preserve">Desktop computers and laptops </v>
+        <v>Manager</v>
       </c>
       <c r="D38" s="13">
         <v>4</v>
@@ -15985,18 +14589,18 @@
       </c>
       <c r="B39" t="str">
         <f>IF(VLOOKUP($A39,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A39,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>People</v>
       </c>
       <c r="C39" t="str">
         <f>IF(VLOOKUP($A39,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A39,Assets!$A:$C,3,FALSE))</f>
-        <v>Printers and scanners</v>
+        <v>Accountants</v>
       </c>
       <c r="D39" s="12">
         <v>1</v>
       </c>
       <c r="E39" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D39,"A",$A39),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T1V1A10</v>
       </c>
       <c r="F39" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D39,"A",$A39),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -16050,11 +14654,11 @@
       </c>
       <c r="B40" t="str">
         <f>IF(VLOOKUP($A40,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A40,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>People</v>
       </c>
       <c r="C40" t="str">
         <f>IF(VLOOKUP($A40,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A40,Assets!$A:$C,3,FALSE))</f>
-        <v>Printers and scanners</v>
+        <v>Accountants</v>
       </c>
       <c r="D40" s="12">
         <v>2</v>
@@ -16115,11 +14719,11 @@
       </c>
       <c r="B41" t="str">
         <f>IF(VLOOKUP($A41,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A41,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>People</v>
       </c>
       <c r="C41" t="str">
         <f>IF(VLOOKUP($A41,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A41,Assets!$A:$C,3,FALSE))</f>
-        <v>Printers and scanners</v>
+        <v>Accountants</v>
       </c>
       <c r="D41" s="12">
         <v>3</v>
@@ -16142,7 +14746,7 @@
       </c>
       <c r="I41" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D41,"A",$A41),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T5V3A10</v>
+        <v/>
       </c>
       <c r="J41" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",J$1,"V",$D41,"A",$A41),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -16180,11 +14784,11 @@
       </c>
       <c r="B42" s="8" t="str">
         <f>IF(VLOOKUP($A42,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A42,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>People</v>
       </c>
       <c r="C42" s="8" t="str">
         <f>IF(VLOOKUP($A42,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A42,Assets!$A:$C,3,FALSE))</f>
-        <v>Printers and scanners</v>
+        <v>Accountants</v>
       </c>
       <c r="D42" s="13">
         <v>4</v>
@@ -16245,18 +14849,18 @@
       </c>
       <c r="B43" t="str">
         <f>IF(VLOOKUP($A43,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A43,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>People</v>
       </c>
       <c r="C43" t="str">
         <f>IF(VLOOKUP($A43,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A43,Assets!$A:$C,3,FALSE))</f>
-        <v>Uninterruptible Power Supplies (UPS)</v>
+        <v>Bookkeeper</v>
       </c>
       <c r="D43" s="12">
         <v>1</v>
       </c>
       <c r="E43" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D43,"A",$A43),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T1V1A11</v>
       </c>
       <c r="F43" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D43,"A",$A43),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -16280,7 +14884,7 @@
       </c>
       <c r="K43" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",K$1,"V",$D43,"A",$A43),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T7V1A11</v>
+        <v/>
       </c>
       <c r="L43" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",L$1,"V",$D43,"A",$A43),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -16310,11 +14914,11 @@
       </c>
       <c r="B44" t="str">
         <f>IF(VLOOKUP($A44,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A44,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>People</v>
       </c>
       <c r="C44" t="str">
         <f>IF(VLOOKUP($A44,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A44,Assets!$A:$C,3,FALSE))</f>
-        <v>Uninterruptible Power Supplies (UPS)</v>
+        <v>Bookkeeper</v>
       </c>
       <c r="D44" s="12">
         <v>2</v>
@@ -16337,7 +14941,7 @@
       </c>
       <c r="I44" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D44,"A",$A44),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T5V2A11</v>
+        <v/>
       </c>
       <c r="J44" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",J$1,"V",$D44,"A",$A44),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -16375,11 +14979,11 @@
       </c>
       <c r="B45" t="str">
         <f>IF(VLOOKUP($A45,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A45,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>People</v>
       </c>
       <c r="C45" t="str">
         <f>IF(VLOOKUP($A45,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A45,Assets!$A:$C,3,FALSE))</f>
-        <v>Uninterruptible Power Supplies (UPS)</v>
+        <v>Bookkeeper</v>
       </c>
       <c r="D45" s="12">
         <v>3</v>
@@ -16440,11 +15044,11 @@
       </c>
       <c r="B46" s="8" t="str">
         <f>IF(VLOOKUP($A46,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A46,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>People</v>
       </c>
       <c r="C46" s="8" t="str">
         <f>IF(VLOOKUP($A46,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A46,Assets!$A:$C,3,FALSE))</f>
-        <v>Uninterruptible Power Supplies (UPS)</v>
+        <v>Bookkeeper</v>
       </c>
       <c r="D46" s="13">
         <v>4</v>
@@ -16505,18 +15109,18 @@
       </c>
       <c r="B47" t="str">
         <f>IF(VLOOKUP($A47,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A47,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>People</v>
       </c>
       <c r="C47" t="str">
         <f>IF(VLOOKUP($A47,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A47,Assets!$A:$C,3,FALSE))</f>
-        <v>Racks, cabling (Ethernet, fibre), patch panels</v>
+        <v>IT Support worker</v>
       </c>
       <c r="D47" s="12">
         <v>1</v>
       </c>
       <c r="E47" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D47,"A",$A47),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T1V1A12</v>
       </c>
       <c r="F47" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D47,"A",$A47),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -16532,7 +15136,7 @@
       </c>
       <c r="I47" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D47,"A",$A47),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T5V1A12</v>
+        <v/>
       </c>
       <c r="J47" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",J$1,"V",$D47,"A",$A47),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -16570,11 +15174,11 @@
       </c>
       <c r="B48" t="str">
         <f>IF(VLOOKUP($A48,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A48,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>People</v>
       </c>
       <c r="C48" t="str">
         <f>IF(VLOOKUP($A48,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A48,Assets!$A:$C,3,FALSE))</f>
-        <v>Racks, cabling (Ethernet, fibre), patch panels</v>
+        <v>IT Support worker</v>
       </c>
       <c r="D48" s="12">
         <v>2</v>
@@ -16605,7 +15209,7 @@
       </c>
       <c r="K48" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",K$1,"V",$D48,"A",$A48),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T7V2A12</v>
+        <v/>
       </c>
       <c r="L48" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",L$1,"V",$D48,"A",$A48),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -16635,11 +15239,11 @@
       </c>
       <c r="B49" t="str">
         <f>IF(VLOOKUP($A49,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A49,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>People</v>
       </c>
       <c r="C49" t="str">
         <f>IF(VLOOKUP($A49,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A49,Assets!$A:$C,3,FALSE))</f>
-        <v>Racks, cabling (Ethernet, fibre), patch panels</v>
+        <v>IT Support worker</v>
       </c>
       <c r="D49" s="12">
         <v>3</v>
@@ -16666,7 +15270,7 @@
       </c>
       <c r="J49" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",J$1,"V",$D49,"A",$A49),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T6V3A12</v>
+        <v/>
       </c>
       <c r="K49" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",K$1,"V",$D49,"A",$A49),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -16700,11 +15304,11 @@
       </c>
       <c r="B50" s="8" t="str">
         <f>IF(VLOOKUP($A50,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A50,Assets!$A:$C,2,FALSE))</f>
-        <v>Hardware</v>
+        <v>People</v>
       </c>
       <c r="C50" s="8" t="str">
         <f>IF(VLOOKUP($A50,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A50,Assets!$A:$C,3,FALSE))</f>
-        <v>Racks, cabling (Ethernet, fibre), patch panels</v>
+        <v>IT Support worker</v>
       </c>
       <c r="D50" s="13">
         <v>4</v>
@@ -16765,11 +15369,11 @@
       </c>
       <c r="B51" t="str">
         <f>IF(VLOOKUP($A51,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A51,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Network</v>
       </c>
       <c r="C51" t="str">
         <f>IF(VLOOKUP($A51,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A51,Assets!$A:$C,3,FALSE))</f>
-        <v>Operating systems (Windows Server, Linux, Windows/macOS clients)</v>
+        <v>LAN 88.1.1.0/24</v>
       </c>
       <c r="D51" s="12">
         <v>1</v>
@@ -16788,7 +15392,7 @@
       </c>
       <c r="H51" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",H$1,"V",$D51,"A",$A51),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T4V1A13</v>
+        <v/>
       </c>
       <c r="I51" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D51,"A",$A51),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -16812,7 +15416,7 @@
       </c>
       <c r="N51" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",N$1,"V",$D51,"A",$A51),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T10V1A13</v>
       </c>
       <c r="O51" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",O$1,"V",$D51,"A",$A51),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -16830,11 +15434,11 @@
       </c>
       <c r="B52" t="str">
         <f>IF(VLOOKUP($A52,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A52,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Network</v>
       </c>
       <c r="C52" t="str">
         <f>IF(VLOOKUP($A52,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A52,Assets!$A:$C,3,FALSE))</f>
-        <v>Operating systems (Windows Server, Linux, Windows/macOS clients)</v>
+        <v>LAN 88.1.1.0/24</v>
       </c>
       <c r="D52" s="12">
         <v>2</v>
@@ -16845,7 +15449,7 @@
       </c>
       <c r="F52" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D52,"A",$A52),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T2V2A13</v>
+        <v/>
       </c>
       <c r="G52" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D52,"A",$A52),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -16895,11 +15499,11 @@
       </c>
       <c r="B53" t="str">
         <f>IF(VLOOKUP($A53,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A53,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Network</v>
       </c>
       <c r="C53" t="str">
         <f>IF(VLOOKUP($A53,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A53,Assets!$A:$C,3,FALSE))</f>
-        <v>Operating systems (Windows Server, Linux, Windows/macOS clients)</v>
+        <v>LAN 88.1.1.0/24</v>
       </c>
       <c r="D53" s="12">
         <v>3</v>
@@ -16960,11 +15564,11 @@
       </c>
       <c r="B54" s="8" t="str">
         <f>IF(VLOOKUP($A54,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A54,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Network</v>
       </c>
       <c r="C54" s="8" t="str">
         <f>IF(VLOOKUP($A54,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A54,Assets!$A:$C,3,FALSE))</f>
-        <v>Operating systems (Windows Server, Linux, Windows/macOS clients)</v>
+        <v>LAN 88.1.1.0/24</v>
       </c>
       <c r="D54" s="13">
         <v>4</v>
@@ -17025,11 +15629,11 @@
       </c>
       <c r="B55" t="str">
         <f>IF(VLOOKUP($A55,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A55,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Network</v>
       </c>
       <c r="C55" t="str">
         <f>IF(VLOOKUP($A55,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A55,Assets!$A:$C,3,FALSE))</f>
-        <v>Accounting and finance software</v>
+        <v>VM network 192.168.56.0/24</v>
       </c>
       <c r="D55" s="12">
         <v>1</v>
@@ -17040,7 +15644,7 @@
       </c>
       <c r="F55" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D55,"A",$A55),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T2V1A14</v>
       </c>
       <c r="G55" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D55,"A",$A55),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -17052,7 +15656,7 @@
       </c>
       <c r="I55" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D55,"A",$A55),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T5V1A14</v>
+        <v/>
       </c>
       <c r="J55" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",J$1,"V",$D55,"A",$A55),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -17090,11 +15694,11 @@
       </c>
       <c r="B56" t="str">
         <f>IF(VLOOKUP($A56,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A56,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Network</v>
       </c>
       <c r="C56" t="str">
         <f>IF(VLOOKUP($A56,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A56,Assets!$A:$C,3,FALSE))</f>
-        <v>Accounting and finance software</v>
+        <v>VM network 192.168.56.0/24</v>
       </c>
       <c r="D56" s="12">
         <v>2</v>
@@ -17155,11 +15759,11 @@
       </c>
       <c r="B57" t="str">
         <f>IF(VLOOKUP($A57,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A57,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Network</v>
       </c>
       <c r="C57" t="str">
         <f>IF(VLOOKUP($A57,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A57,Assets!$A:$C,3,FALSE))</f>
-        <v>Accounting and finance software</v>
+        <v>VM network 192.168.56.0/24</v>
       </c>
       <c r="D57" s="12">
         <v>3</v>
@@ -17220,11 +15824,11 @@
       </c>
       <c r="B58" s="8" t="str">
         <f>IF(VLOOKUP($A58,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A58,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Network</v>
       </c>
       <c r="C58" s="8" t="str">
         <f>IF(VLOOKUP($A58,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A58,Assets!$A:$C,3,FALSE))</f>
-        <v>Accounting and finance software</v>
+        <v>VM network 192.168.56.0/24</v>
       </c>
       <c r="D58" s="13">
         <v>4</v>
@@ -17285,11 +15889,11 @@
       </c>
       <c r="B59" t="str">
         <f>IF(VLOOKUP($A59,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A59,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Network</v>
       </c>
       <c r="C59" t="str">
         <f>IF(VLOOKUP($A59,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A59,Assets!$A:$C,3,FALSE))</f>
-        <v>Security software (antivirus, endpoint protection)</v>
+        <v>WAN Connection 10.0.3.15/24</v>
       </c>
       <c r="D59" s="12">
         <v>1</v>
@@ -17312,7 +15916,7 @@
       </c>
       <c r="I59" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D59,"A",$A59),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T5V1A15</v>
+        <v/>
       </c>
       <c r="J59" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",J$1,"V",$D59,"A",$A59),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -17350,11 +15954,11 @@
       </c>
       <c r="B60" t="str">
         <f>IF(VLOOKUP($A60,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A60,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Network</v>
       </c>
       <c r="C60" t="str">
         <f>IF(VLOOKUP($A60,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A60,Assets!$A:$C,3,FALSE))</f>
-        <v>Security software (antivirus, endpoint protection)</v>
+        <v>WAN Connection 10.0.3.15/24</v>
       </c>
       <c r="D60" s="12">
         <v>2</v>
@@ -17415,18 +16019,18 @@
       </c>
       <c r="B61" t="str">
         <f>IF(VLOOKUP($A61,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A61,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Network</v>
       </c>
       <c r="C61" t="str">
         <f>IF(VLOOKUP($A61,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A61,Assets!$A:$C,3,FALSE))</f>
-        <v>Security software (antivirus, endpoint protection)</v>
+        <v>WAN Connection 10.0.3.15/24</v>
       </c>
       <c r="D61" s="12">
         <v>3</v>
       </c>
       <c r="E61" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D61,"A",$A61),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T1V3A15</v>
       </c>
       <c r="F61" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D61,"A",$A61),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -17480,11 +16084,11 @@
       </c>
       <c r="B62" s="8" t="str">
         <f>IF(VLOOKUP($A62,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A62,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Network</v>
       </c>
       <c r="C62" s="8" t="str">
         <f>IF(VLOOKUP($A62,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A62,Assets!$A:$C,3,FALSE))</f>
-        <v>Security software (antivirus, endpoint protection)</v>
+        <v>WAN Connection 10.0.3.15/24</v>
       </c>
       <c r="D62" s="13">
         <v>4</v>
@@ -17545,11 +16149,11 @@
       </c>
       <c r="B63" t="str">
         <f>IF(VLOOKUP($A63,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A63,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Data</v>
       </c>
       <c r="C63" t="str">
         <f>IF(VLOOKUP($A63,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A63,Assets!$A:$C,3,FALSE))</f>
-        <v>Website and web applications</v>
+        <v>Client Tax Records</v>
       </c>
       <c r="D63" s="12">
         <v>1</v>
@@ -17560,11 +16164,11 @@
       </c>
       <c r="F63" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D63,"A",$A63),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T2V1A16</v>
+        <v/>
       </c>
       <c r="G63" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D63,"A",$A63),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T3V1A16</v>
       </c>
       <c r="H63" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",H$1,"V",$D63,"A",$A63),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -17610,11 +16214,11 @@
       </c>
       <c r="B64" t="str">
         <f>IF(VLOOKUP($A64,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A64,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Data</v>
       </c>
       <c r="C64" t="str">
         <f>IF(VLOOKUP($A64,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A64,Assets!$A:$C,3,FALSE))</f>
-        <v>Website and web applications</v>
+        <v>Client Tax Records</v>
       </c>
       <c r="D64" s="12">
         <v>2</v>
@@ -17653,7 +16257,7 @@
       </c>
       <c r="M64" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",M$1,"V",$D64,"A",$A64),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T9V2A16</v>
+        <v/>
       </c>
       <c r="N64" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",N$1,"V",$D64,"A",$A64),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -17675,11 +16279,11 @@
       </c>
       <c r="B65" t="str">
         <f>IF(VLOOKUP($A65,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A65,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Data</v>
       </c>
       <c r="C65" t="str">
         <f>IF(VLOOKUP($A65,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A65,Assets!$A:$C,3,FALSE))</f>
-        <v>Website and web applications</v>
+        <v>Client Tax Records</v>
       </c>
       <c r="D65" s="12">
         <v>3</v>
@@ -17740,11 +16344,11 @@
       </c>
       <c r="B66" s="8" t="str">
         <f>IF(VLOOKUP($A66,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A66,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Data</v>
       </c>
       <c r="C66" s="8" t="str">
         <f>IF(VLOOKUP($A66,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A66,Assets!$A:$C,3,FALSE))</f>
-        <v>Website and web applications</v>
+        <v>Client Tax Records</v>
       </c>
       <c r="D66" s="13">
         <v>4</v>
@@ -17805,22 +16409,22 @@
       </c>
       <c r="B67" t="str">
         <f>IF(VLOOKUP($A67,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A67,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Data</v>
       </c>
       <c r="C67" t="str">
         <f>IF(VLOOKUP($A67,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A67,Assets!$A:$C,3,FALSE))</f>
-        <v>CRM software</v>
+        <v>Payroll Data</v>
       </c>
       <c r="D67" s="12">
         <v>1</v>
       </c>
       <c r="E67" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D67,"A",$A67),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T1V1A17</v>
       </c>
       <c r="F67" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D67,"A",$A67),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T2V1A17</v>
+        <v/>
       </c>
       <c r="G67" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D67,"A",$A67),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -17870,18 +16474,18 @@
       </c>
       <c r="B68" t="str">
         <f>IF(VLOOKUP($A68,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A68,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Data</v>
       </c>
       <c r="C68" t="str">
         <f>IF(VLOOKUP($A68,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A68,Assets!$A:$C,3,FALSE))</f>
-        <v>CRM software</v>
+        <v>Payroll Data</v>
       </c>
       <c r="D68" s="12">
         <v>2</v>
       </c>
       <c r="E68" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D68,"A",$A68),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V2A17</v>
+        <v/>
       </c>
       <c r="F68" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D68,"A",$A68),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -17935,11 +16539,11 @@
       </c>
       <c r="B69" t="str">
         <f>IF(VLOOKUP($A69,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A69,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Data</v>
       </c>
       <c r="C69" t="str">
         <f>IF(VLOOKUP($A69,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A69,Assets!$A:$C,3,FALSE))</f>
-        <v>CRM software</v>
+        <v>Payroll Data</v>
       </c>
       <c r="D69" s="12">
         <v>3</v>
@@ -17978,7 +16582,7 @@
       </c>
       <c r="M69" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",M$1,"V",$D69,"A",$A69),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T9V3A17</v>
+        <v/>
       </c>
       <c r="N69" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",N$1,"V",$D69,"A",$A69),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -18000,11 +16604,11 @@
       </c>
       <c r="B70" s="8" t="str">
         <f>IF(VLOOKUP($A70,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A70,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Data</v>
       </c>
       <c r="C70" s="8" t="str">
         <f>IF(VLOOKUP($A70,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A70,Assets!$A:$C,3,FALSE))</f>
-        <v>CRM software</v>
+        <v>Payroll Data</v>
       </c>
       <c r="D70" s="13">
         <v>4</v>
@@ -18065,11 +16669,11 @@
       </c>
       <c r="B71" t="str">
         <f>IF(VLOOKUP($A71,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A71,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Data</v>
       </c>
       <c r="C71" t="str">
         <f>IF(VLOOKUP($A71,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A71,Assets!$A:$C,3,FALSE))</f>
-        <v>Security software (antivirus, endpoint protection)</v>
+        <v>Financial Statements</v>
       </c>
       <c r="D71" s="12">
         <v>1</v>
@@ -18080,7 +16684,7 @@
       </c>
       <c r="F71" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D71,"A",$A71),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T2V1A18</v>
       </c>
       <c r="G71" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D71,"A",$A71),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -18108,7 +16712,7 @@
       </c>
       <c r="M71" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",M$1,"V",$D71,"A",$A71),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T9V1A18</v>
+        <v/>
       </c>
       <c r="N71" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",N$1,"V",$D71,"A",$A71),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -18130,11 +16734,11 @@
       </c>
       <c r="B72" t="str">
         <f>IF(VLOOKUP($A72,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A72,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Data</v>
       </c>
       <c r="C72" t="str">
         <f>IF(VLOOKUP($A72,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A72,Assets!$A:$C,3,FALSE))</f>
-        <v>Security software (antivirus, endpoint protection)</v>
+        <v>Financial Statements</v>
       </c>
       <c r="D72" s="12">
         <v>2</v>
@@ -18161,7 +16765,7 @@
       </c>
       <c r="J72" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",J$1,"V",$D72,"A",$A72),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T6V2A18</v>
+        <v/>
       </c>
       <c r="K72" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",K$1,"V",$D72,"A",$A72),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -18195,11 +16799,11 @@
       </c>
       <c r="B73" t="str">
         <f>IF(VLOOKUP($A73,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A73,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Data</v>
       </c>
       <c r="C73" t="str">
         <f>IF(VLOOKUP($A73,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A73,Assets!$A:$C,3,FALSE))</f>
-        <v>Security software (antivirus, endpoint protection)</v>
+        <v>Financial Statements</v>
       </c>
       <c r="D73" s="12">
         <v>3</v>
@@ -18260,11 +16864,11 @@
       </c>
       <c r="B74" s="8" t="str">
         <f>IF(VLOOKUP($A74,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A74,Assets!$A:$C,2,FALSE))</f>
-        <v>Software</v>
+        <v>Data</v>
       </c>
       <c r="C74" s="8" t="str">
         <f>IF(VLOOKUP($A74,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A74,Assets!$A:$C,3,FALSE))</f>
-        <v>Security software (antivirus, endpoint protection)</v>
+        <v>Financial Statements</v>
       </c>
       <c r="D74" s="13">
         <v>4</v>
@@ -18325,18 +16929,18 @@
       </c>
       <c r="B75" t="str">
         <f>IF(VLOOKUP($A75,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A75,Assets!$A:$C,2,FALSE))</f>
-        <v>Network</v>
+        <v>Data</v>
       </c>
       <c r="C75" t="str">
         <f>IF(VLOOKUP($A75,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A75,Assets!$A:$C,3,FALSE))</f>
-        <v>Network management and monitoring tools</v>
+        <v>Website content</v>
       </c>
       <c r="D75" s="12">
         <v>1</v>
       </c>
       <c r="E75" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D75,"A",$A75),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V1A19</v>
+        <v/>
       </c>
       <c r="F75" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D75,"A",$A75),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -18376,7 +16980,7 @@
       </c>
       <c r="O75" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",O$1,"V",$D75,"A",$A75),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T11V1A19</v>
       </c>
       <c r="P75" s="12" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",P$1,"V",$D75,"A",$A75),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -18390,11 +16994,11 @@
       </c>
       <c r="B76" t="str">
         <f>IF(VLOOKUP($A76,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A76,Assets!$A:$C,2,FALSE))</f>
-        <v>Network</v>
+        <v>Data</v>
       </c>
       <c r="C76" t="str">
         <f>IF(VLOOKUP($A76,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A76,Assets!$A:$C,3,FALSE))</f>
-        <v>Network management and monitoring tools</v>
+        <v>Website content</v>
       </c>
       <c r="D76" s="12">
         <v>2</v>
@@ -18405,7 +17009,7 @@
       </c>
       <c r="F76" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D76,"A",$A76),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T2V2A19</v>
+        <v/>
       </c>
       <c r="G76" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D76,"A",$A76),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -18455,11 +17059,11 @@
       </c>
       <c r="B77" t="str">
         <f>IF(VLOOKUP($A77,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A77,Assets!$A:$C,2,FALSE))</f>
-        <v>Network</v>
+        <v>Data</v>
       </c>
       <c r="C77" t="str">
         <f>IF(VLOOKUP($A77,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A77,Assets!$A:$C,3,FALSE))</f>
-        <v>Network management and monitoring tools</v>
+        <v>Website content</v>
       </c>
       <c r="D77" s="12">
         <v>3</v>
@@ -18494,7 +17098,7 @@
       </c>
       <c r="L77" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",L$1,"V",$D77,"A",$A77),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T8V3A19</v>
+        <v/>
       </c>
       <c r="M77" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",M$1,"V",$D77,"A",$A77),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -18520,11 +17124,11 @@
       </c>
       <c r="B78" s="8" t="str">
         <f>IF(VLOOKUP($A78,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A78,Assets!$A:$C,2,FALSE))</f>
-        <v>Network</v>
+        <v>Data</v>
       </c>
       <c r="C78" s="8" t="str">
         <f>IF(VLOOKUP($A78,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A78,Assets!$A:$C,3,FALSE))</f>
-        <v>Network management and monitoring tools</v>
+        <v>Website content</v>
       </c>
       <c r="D78" s="13">
         <v>4</v>
@@ -18585,18 +17189,18 @@
       </c>
       <c r="B79" t="str">
         <f>IF(VLOOKUP($A79,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A79,Assets!$A:$C,2,FALSE))</f>
-        <v>Network</v>
+        <v>Processes</v>
       </c>
       <c r="C79" t="str">
         <f>IF(VLOOKUP($A79,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A79,Assets!$A:$C,3,FALSE))</f>
-        <v>Internet connections (ISP)</v>
+        <v>Firewall management</v>
       </c>
       <c r="D79" s="12">
         <v>1</v>
       </c>
       <c r="E79" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D79,"A",$A79),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T1V1A20</v>
       </c>
       <c r="F79" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D79,"A",$A79),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -18632,7 +17236,7 @@
       </c>
       <c r="N79" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",N$1,"V",$D79,"A",$A79),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T10V1A20</v>
+        <v/>
       </c>
       <c r="O79" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",O$1,"V",$D79,"A",$A79),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -18650,11 +17254,11 @@
       </c>
       <c r="B80" t="str">
         <f>IF(VLOOKUP($A80,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A80,Assets!$A:$C,2,FALSE))</f>
-        <v>Network</v>
+        <v>Processes</v>
       </c>
       <c r="C80" t="str">
         <f>IF(VLOOKUP($A80,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A80,Assets!$A:$C,3,FALSE))</f>
-        <v>Internet connections (ISP)</v>
+        <v>Firewall management</v>
       </c>
       <c r="D80" s="12">
         <v>2</v>
@@ -18689,7 +17293,7 @@
       </c>
       <c r="L80" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",L$1,"V",$D80,"A",$A80),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T8V2A20</v>
+        <v/>
       </c>
       <c r="M80" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",M$1,"V",$D80,"A",$A80),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -18715,11 +17319,11 @@
       </c>
       <c r="B81" t="str">
         <f>IF(VLOOKUP($A81,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A81,Assets!$A:$C,2,FALSE))</f>
-        <v>Network</v>
+        <v>Processes</v>
       </c>
       <c r="C81" t="str">
         <f>IF(VLOOKUP($A81,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A81,Assets!$A:$C,3,FALSE))</f>
-        <v>Internet connections (ISP)</v>
+        <v>Firewall management</v>
       </c>
       <c r="D81" s="12">
         <v>3</v>
@@ -18780,11 +17384,11 @@
       </c>
       <c r="B82" s="8" t="str">
         <f>IF(VLOOKUP($A82,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A82,Assets!$A:$C,2,FALSE))</f>
-        <v>Network</v>
+        <v>Processes</v>
       </c>
       <c r="C82" s="8" t="str">
         <f>IF(VLOOKUP($A82,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A82,Assets!$A:$C,3,FALSE))</f>
-        <v>Internet connections (ISP)</v>
+        <v>Firewall management</v>
       </c>
       <c r="D82" s="13">
         <v>4</v>
@@ -18845,18 +17449,18 @@
       </c>
       <c r="B83" t="str">
         <f>IF(VLOOKUP($A83,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A83,Assets!$A:$C,2,FALSE))</f>
-        <v>Network</v>
+        <v>Processes</v>
       </c>
       <c r="C83" t="str">
         <f>IF(VLOOKUP($A83,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A83,Assets!$A:$C,3,FALSE))</f>
-        <v>Firewalls and security gateways</v>
+        <v>Access to the SSH server</v>
       </c>
       <c r="D83" s="12">
         <v>1</v>
       </c>
       <c r="E83" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D83,"A",$A83),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V1A21</v>
+        <v/>
       </c>
       <c r="F83" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D83,"A",$A83),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -18868,7 +17472,7 @@
       </c>
       <c r="H83" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",H$1,"V",$D83,"A",$A83),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T4V1A21</v>
       </c>
       <c r="I83" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D83,"A",$A83),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -18910,11 +17514,11 @@
       </c>
       <c r="B84" t="str">
         <f>IF(VLOOKUP($A84,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A84,Assets!$A:$C,2,FALSE))</f>
-        <v>Network</v>
+        <v>Processes</v>
       </c>
       <c r="C84" t="str">
         <f>IF(VLOOKUP($A84,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A84,Assets!$A:$C,3,FALSE))</f>
-        <v>Firewalls and security gateways</v>
+        <v>Access to the SSH server</v>
       </c>
       <c r="D84" s="12">
         <v>2</v>
@@ -18925,7 +17529,7 @@
       </c>
       <c r="F84" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D84,"A",$A84),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T2V2A21</v>
+        <v/>
       </c>
       <c r="G84" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D84,"A",$A84),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -18975,11 +17579,11 @@
       </c>
       <c r="B85" t="str">
         <f>IF(VLOOKUP($A85,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A85,Assets!$A:$C,2,FALSE))</f>
-        <v>Network</v>
+        <v>Processes</v>
       </c>
       <c r="C85" t="str">
         <f>IF(VLOOKUP($A85,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A85,Assets!$A:$C,3,FALSE))</f>
-        <v>Firewalls and security gateways</v>
+        <v>Access to the SSH server</v>
       </c>
       <c r="D85" s="12">
         <v>3</v>
@@ -19014,7 +17618,7 @@
       </c>
       <c r="L85" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",L$1,"V",$D85,"A",$A85),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T8V3A21</v>
+        <v/>
       </c>
       <c r="M85" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",M$1,"V",$D85,"A",$A85),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -19040,11 +17644,11 @@
       </c>
       <c r="B86" s="8" t="str">
         <f>IF(VLOOKUP($A86,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A86,Assets!$A:$C,2,FALSE))</f>
-        <v>Network</v>
+        <v>Processes</v>
       </c>
       <c r="C86" s="8" t="str">
         <f>IF(VLOOKUP($A86,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A86,Assets!$A:$C,3,FALSE))</f>
-        <v>Firewalls and security gateways</v>
+        <v>Access to the SSH server</v>
       </c>
       <c r="D86" s="13">
         <v>4</v>
@@ -19105,11 +17709,11 @@
       </c>
       <c r="B87" t="str">
         <f>IF(VLOOKUP($A87,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A87,Assets!$A:$C,2,FALSE))</f>
-        <v>Network</v>
+        <v>Processes</v>
       </c>
       <c r="C87" t="str">
         <f>IF(VLOOKUP($A87,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A87,Assets!$A:$C,3,FALSE))</f>
-        <v>Wireless networks</v>
+        <v>Backup procedure</v>
       </c>
       <c r="D87" s="12">
         <v>1</v>
@@ -19128,7 +17732,7 @@
       </c>
       <c r="H87" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",H$1,"V",$D87,"A",$A87),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T4V1A22</v>
+        <v/>
       </c>
       <c r="I87" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D87,"A",$A87),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -19148,7 +17752,7 @@
       </c>
       <c r="M87" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",M$1,"V",$D87,"A",$A87),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T9V1A22</v>
       </c>
       <c r="N87" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",N$1,"V",$D87,"A",$A87),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -19170,18 +17774,18 @@
       </c>
       <c r="B88" t="str">
         <f>IF(VLOOKUP($A88,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A88,Assets!$A:$C,2,FALSE))</f>
-        <v>Network</v>
+        <v>Processes</v>
       </c>
       <c r="C88" t="str">
         <f>IF(VLOOKUP($A88,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A88,Assets!$A:$C,3,FALSE))</f>
-        <v>Wireless networks</v>
+        <v>Backup procedure</v>
       </c>
       <c r="D88" s="12">
         <v>2</v>
       </c>
       <c r="E88" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D88,"A",$A88),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V2A22</v>
+        <v/>
       </c>
       <c r="F88" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D88,"A",$A88),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -19197,7 +17801,7 @@
       </c>
       <c r="I88" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D88,"A",$A88),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v/>
+        <v>T5V2A22</v>
       </c>
       <c r="J88" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",J$1,"V",$D88,"A",$A88),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -19235,11 +17839,11 @@
       </c>
       <c r="B89" t="str">
         <f>IF(VLOOKUP($A89,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A89,Assets!$A:$C,2,FALSE))</f>
-        <v>Network</v>
+        <v>Processes</v>
       </c>
       <c r="C89" t="str">
         <f>IF(VLOOKUP($A89,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A89,Assets!$A:$C,3,FALSE))</f>
-        <v>Wireless networks</v>
+        <v>Backup procedure</v>
       </c>
       <c r="D89" s="12">
         <v>3</v>
@@ -19250,7 +17854,7 @@
       </c>
       <c r="F89" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D89,"A",$A89),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T2V3A22</v>
+        <v/>
       </c>
       <c r="G89" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D89,"A",$A89),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -19300,11 +17904,11 @@
       </c>
       <c r="B90" s="8" t="str">
         <f>IF(VLOOKUP($A90,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A90,Assets!$A:$C,2,FALSE))</f>
-        <v>Network</v>
+        <v>Processes</v>
       </c>
       <c r="C90" s="8" t="str">
         <f>IF(VLOOKUP($A90,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A90,Assets!$A:$C,3,FALSE))</f>
-        <v>Wireless networks</v>
+        <v>Backup procedure</v>
       </c>
       <c r="D90" s="13">
         <v>4</v>
@@ -19365,18 +17969,18 @@
       </c>
       <c r="B91" t="str">
         <f>IF(VLOOKUP($A91,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A91,Assets!$A:$C,2,FALSE))</f>
-        <v>Network</v>
+        <v/>
       </c>
       <c r="C91" t="str">
         <f>IF(VLOOKUP($A91,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A91,Assets!$A:$C,3,FALSE))</f>
-        <v>Network addressing</v>
+        <v/>
       </c>
       <c r="D91" s="12">
         <v>1</v>
       </c>
       <c r="E91" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D91,"A",$A91),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V1A23</v>
+        <v/>
       </c>
       <c r="F91" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D91,"A",$A91),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -19430,11 +18034,11 @@
       </c>
       <c r="B92" t="str">
         <f>IF(VLOOKUP($A92,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A92,Assets!$A:$C,2,FALSE))</f>
-        <v>Network</v>
+        <v/>
       </c>
       <c r="C92" t="str">
         <f>IF(VLOOKUP($A92,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A92,Assets!$A:$C,3,FALSE))</f>
-        <v>Network addressing</v>
+        <v/>
       </c>
       <c r="D92" s="12">
         <v>2</v>
@@ -19473,7 +18077,7 @@
       </c>
       <c r="M92" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",M$1,"V",$D92,"A",$A92),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T9V2A23</v>
+        <v/>
       </c>
       <c r="N92" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",N$1,"V",$D92,"A",$A92),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -19495,11 +18099,11 @@
       </c>
       <c r="B93" t="str">
         <f>IF(VLOOKUP($A93,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A93,Assets!$A:$C,2,FALSE))</f>
-        <v>Network</v>
+        <v/>
       </c>
       <c r="C93" t="str">
         <f>IF(VLOOKUP($A93,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A93,Assets!$A:$C,3,FALSE))</f>
-        <v>Network addressing</v>
+        <v/>
       </c>
       <c r="D93" s="12">
         <v>3</v>
@@ -19560,11 +18164,11 @@
       </c>
       <c r="B94" s="8" t="str">
         <f>IF(VLOOKUP($A94,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A94,Assets!$A:$C,2,FALSE))</f>
-        <v>Network</v>
+        <v/>
       </c>
       <c r="C94" s="8" t="str">
         <f>IF(VLOOKUP($A94,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A94,Assets!$A:$C,3,FALSE))</f>
-        <v>Network addressing</v>
+        <v/>
       </c>
       <c r="D94" s="13">
         <v>4</v>
@@ -19625,18 +18229,18 @@
       </c>
       <c r="B95" t="str">
         <f>IF(VLOOKUP($A95,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A95,Assets!$A:$C,2,FALSE))</f>
-        <v>People</v>
+        <v/>
       </c>
       <c r="C95" t="str">
         <f>IF(VLOOKUP($A95,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A95,Assets!$A:$C,3,FALSE))</f>
-        <v>Management</v>
+        <v/>
       </c>
       <c r="D95" s="12">
         <v>1</v>
       </c>
       <c r="E95" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D95,"A",$A95),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V1A24</v>
+        <v/>
       </c>
       <c r="F95" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D95,"A",$A95),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -19690,11 +18294,11 @@
       </c>
       <c r="B96" t="str">
         <f>IF(VLOOKUP($A96,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A96,Assets!$A:$C,2,FALSE))</f>
-        <v>People</v>
+        <v/>
       </c>
       <c r="C96" t="str">
         <f>IF(VLOOKUP($A96,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A96,Assets!$A:$C,3,FALSE))</f>
-        <v>Management</v>
+        <v/>
       </c>
       <c r="D96" s="12">
         <v>2</v>
@@ -19709,7 +18313,7 @@
       </c>
       <c r="G96" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D96,"A",$A96),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T3V2A24</v>
+        <v/>
       </c>
       <c r="H96" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",H$1,"V",$D96,"A",$A96),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -19755,11 +18359,11 @@
       </c>
       <c r="B97" t="str">
         <f>IF(VLOOKUP($A97,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A97,Assets!$A:$C,2,FALSE))</f>
-        <v>People</v>
+        <v/>
       </c>
       <c r="C97" t="str">
         <f>IF(VLOOKUP($A97,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A97,Assets!$A:$C,3,FALSE))</f>
-        <v>Management</v>
+        <v/>
       </c>
       <c r="D97" s="12">
         <v>3</v>
@@ -19820,11 +18424,11 @@
       </c>
       <c r="B98" s="8" t="str">
         <f>IF(VLOOKUP($A98,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A98,Assets!$A:$C,2,FALSE))</f>
-        <v>People</v>
+        <v/>
       </c>
       <c r="C98" s="8" t="str">
         <f>IF(VLOOKUP($A98,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A98,Assets!$A:$C,3,FALSE))</f>
-        <v>Management</v>
+        <v/>
       </c>
       <c r="D98" s="13">
         <v>4</v>
@@ -19885,18 +18489,18 @@
       </c>
       <c r="B99" t="str">
         <f>IF(VLOOKUP($A99,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A99,Assets!$A:$C,2,FALSE))</f>
-        <v>People</v>
+        <v/>
       </c>
       <c r="C99" t="str">
         <f>IF(VLOOKUP($A99,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A99,Assets!$A:$C,3,FALSE))</f>
-        <v xml:space="preserve">Staff </v>
+        <v/>
       </c>
       <c r="D99" s="12">
         <v>1</v>
       </c>
       <c r="E99" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D99,"A",$A99),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V1A25</v>
+        <v/>
       </c>
       <c r="F99" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D99,"A",$A99),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -19950,11 +18554,11 @@
       </c>
       <c r="B100" t="str">
         <f>IF(VLOOKUP($A100,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A100,Assets!$A:$C,2,FALSE))</f>
-        <v>People</v>
+        <v/>
       </c>
       <c r="C100" t="str">
         <f>IF(VLOOKUP($A100,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A100,Assets!$A:$C,3,FALSE))</f>
-        <v xml:space="preserve">Staff </v>
+        <v/>
       </c>
       <c r="D100" s="12">
         <v>2</v>
@@ -19977,7 +18581,7 @@
       </c>
       <c r="I100" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D100,"A",$A100),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T5V2A25</v>
+        <v/>
       </c>
       <c r="J100" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",J$1,"V",$D100,"A",$A100),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -20015,11 +18619,11 @@
       </c>
       <c r="B101" t="str">
         <f>IF(VLOOKUP($A101,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A101,Assets!$A:$C,2,FALSE))</f>
-        <v>People</v>
+        <v/>
       </c>
       <c r="C101" t="str">
         <f>IF(VLOOKUP($A101,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A101,Assets!$A:$C,3,FALSE))</f>
-        <v xml:space="preserve">Staff </v>
+        <v/>
       </c>
       <c r="D101" s="12">
         <v>3</v>
@@ -20080,11 +18684,11 @@
       </c>
       <c r="B102" s="8" t="str">
         <f>IF(VLOOKUP($A102,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A102,Assets!$A:$C,2,FALSE))</f>
-        <v>People</v>
+        <v/>
       </c>
       <c r="C102" s="8" t="str">
         <f>IF(VLOOKUP($A102,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A102,Assets!$A:$C,3,FALSE))</f>
-        <v xml:space="preserve">Staff </v>
+        <v/>
       </c>
       <c r="D102" s="13">
         <v>4</v>
@@ -20145,11 +18749,11 @@
       </c>
       <c r="B103" t="str">
         <f>IF(VLOOKUP($A103,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A103,Assets!$A:$C,2,FALSE))</f>
-        <v>People</v>
+        <v/>
       </c>
       <c r="C103" t="str">
         <f>IF(VLOOKUP($A103,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A103,Assets!$A:$C,3,FALSE))</f>
-        <v>Customers</v>
+        <v/>
       </c>
       <c r="D103" s="12">
         <v>1</v>
@@ -20160,7 +18764,7 @@
       </c>
       <c r="F103" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D103,"A",$A103),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T2V1A26</v>
+        <v/>
       </c>
       <c r="G103" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D103,"A",$A103),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -20210,11 +18814,11 @@
       </c>
       <c r="B104" t="str">
         <f>IF(VLOOKUP($A104,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A104,Assets!$A:$C,2,FALSE))</f>
-        <v>People</v>
+        <v/>
       </c>
       <c r="C104" t="str">
         <f>IF(VLOOKUP($A104,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A104,Assets!$A:$C,3,FALSE))</f>
-        <v>Customers</v>
+        <v/>
       </c>
       <c r="D104" s="12">
         <v>2</v>
@@ -20229,7 +18833,7 @@
       </c>
       <c r="G104" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",G$1,"V",$D104,"A",$A104),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T3V2A26</v>
+        <v/>
       </c>
       <c r="H104" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",H$1,"V",$D104,"A",$A104),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -20275,11 +18879,11 @@
       </c>
       <c r="B105" t="str">
         <f>IF(VLOOKUP($A105,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A105,Assets!$A:$C,2,FALSE))</f>
-        <v>People</v>
+        <v/>
       </c>
       <c r="C105" t="str">
         <f>IF(VLOOKUP($A105,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A105,Assets!$A:$C,3,FALSE))</f>
-        <v>Customers</v>
+        <v/>
       </c>
       <c r="D105" s="12">
         <v>3</v>
@@ -20340,11 +18944,11 @@
       </c>
       <c r="B106" s="8" t="str">
         <f>IF(VLOOKUP($A106,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A106,Assets!$A:$C,2,FALSE))</f>
-        <v>People</v>
+        <v/>
       </c>
       <c r="C106" s="8" t="str">
         <f>IF(VLOOKUP($A106,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A106,Assets!$A:$C,3,FALSE))</f>
-        <v>Customers</v>
+        <v/>
       </c>
       <c r="D106" s="13">
         <v>4</v>
@@ -20405,18 +19009,18 @@
       </c>
       <c r="B107" t="str">
         <f>IF(VLOOKUP($A107,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A107,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C107" t="str">
         <f>IF(VLOOKUP($A107,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A107,Assets!$A:$C,3,FALSE))</f>
-        <v>Network design and configuration processes</v>
+        <v/>
       </c>
       <c r="D107" s="12">
         <v>1</v>
       </c>
       <c r="E107" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D107,"A",$A107),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V1A27</v>
+        <v/>
       </c>
       <c r="F107" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D107,"A",$A107),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -20470,11 +19074,11 @@
       </c>
       <c r="B108" t="str">
         <f>IF(VLOOKUP($A108,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A108,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C108" t="str">
         <f>IF(VLOOKUP($A108,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A108,Assets!$A:$C,3,FALSE))</f>
-        <v>Network design and configuration processes</v>
+        <v/>
       </c>
       <c r="D108" s="12">
         <v>2</v>
@@ -20501,7 +19105,7 @@
       </c>
       <c r="J108" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",J$1,"V",$D108,"A",$A108),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T6V2A27</v>
+        <v/>
       </c>
       <c r="K108" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",K$1,"V",$D108,"A",$A108),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -20535,11 +19139,11 @@
       </c>
       <c r="B109" t="str">
         <f>IF(VLOOKUP($A109,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A109,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C109" t="str">
         <f>IF(VLOOKUP($A109,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A109,Assets!$A:$C,3,FALSE))</f>
-        <v>Network design and configuration processes</v>
+        <v/>
       </c>
       <c r="D109" s="12">
         <v>3</v>
@@ -20600,11 +19204,11 @@
       </c>
       <c r="B110" s="8" t="str">
         <f>IF(VLOOKUP($A110,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A110,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C110" s="8" t="str">
         <f>IF(VLOOKUP($A110,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A110,Assets!$A:$C,3,FALSE))</f>
-        <v>Network design and configuration processes</v>
+        <v/>
       </c>
       <c r="D110" s="13">
         <v>4</v>
@@ -20665,18 +19269,18 @@
       </c>
       <c r="B111" t="str">
         <f>IF(VLOOKUP($A111,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A111,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C111" t="str">
         <f>IF(VLOOKUP($A111,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A111,Assets!$A:$C,3,FALSE))</f>
-        <v>Access control and identity management processes</v>
+        <v/>
       </c>
       <c r="D111" s="12">
         <v>1</v>
       </c>
       <c r="E111" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D111,"A",$A111),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V1A28</v>
+        <v/>
       </c>
       <c r="F111" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D111,"A",$A111),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -20730,11 +19334,11 @@
       </c>
       <c r="B112" t="str">
         <f>IF(VLOOKUP($A112,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A112,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C112" t="str">
         <f>IF(VLOOKUP($A112,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A112,Assets!$A:$C,3,FALSE))</f>
-        <v>Access control and identity management processes</v>
+        <v/>
       </c>
       <c r="D112" s="12">
         <v>2</v>
@@ -20753,7 +19357,7 @@
       </c>
       <c r="H112" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",H$1,"V",$D112,"A",$A112),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T4V2A28</v>
+        <v/>
       </c>
       <c r="I112" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D112,"A",$A112),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -20795,11 +19399,11 @@
       </c>
       <c r="B113" t="str">
         <f>IF(VLOOKUP($A113,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A113,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C113" t="str">
         <f>IF(VLOOKUP($A113,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A113,Assets!$A:$C,3,FALSE))</f>
-        <v>Access control and identity management processes</v>
+        <v/>
       </c>
       <c r="D113" s="12">
         <v>3</v>
@@ -20860,11 +19464,11 @@
       </c>
       <c r="B114" s="8" t="str">
         <f>IF(VLOOKUP($A114,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A114,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C114" s="8" t="str">
         <f>IF(VLOOKUP($A114,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A114,Assets!$A:$C,3,FALSE))</f>
-        <v>Access control and identity management processes</v>
+        <v/>
       </c>
       <c r="D114" s="13">
         <v>4</v>
@@ -20925,11 +19529,11 @@
       </c>
       <c r="B115" t="str">
         <f>IF(VLOOKUP($A115,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A115,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C115" t="str">
         <f>IF(VLOOKUP($A115,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A115,Assets!$A:$C,3,FALSE))</f>
-        <v>Data backup and disaster recovery procedures</v>
+        <v/>
       </c>
       <c r="D115" s="12">
         <v>1</v>
@@ -20968,7 +19572,7 @@
       </c>
       <c r="M115" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",M$1,"V",$D115,"A",$A115),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T9V1A29</v>
+        <v/>
       </c>
       <c r="N115" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",N$1,"V",$D115,"A",$A115),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -20990,18 +19594,18 @@
       </c>
       <c r="B116" t="str">
         <f>IF(VLOOKUP($A116,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A116,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C116" t="str">
         <f>IF(VLOOKUP($A116,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A116,Assets!$A:$C,3,FALSE))</f>
-        <v>Data backup and disaster recovery procedures</v>
+        <v/>
       </c>
       <c r="D116" s="12">
         <v>2</v>
       </c>
       <c r="E116" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D116,"A",$A116),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V2A29</v>
+        <v/>
       </c>
       <c r="F116" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D116,"A",$A116),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -21055,11 +19659,11 @@
       </c>
       <c r="B117" t="str">
         <f>IF(VLOOKUP($A117,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A117,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C117" t="str">
         <f>IF(VLOOKUP($A117,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A117,Assets!$A:$C,3,FALSE))</f>
-        <v>Data backup and disaster recovery procedures</v>
+        <v/>
       </c>
       <c r="D117" s="12">
         <v>3</v>
@@ -21090,7 +19694,7 @@
       </c>
       <c r="K117" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",K$1,"V",$D117,"A",$A117),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T7V3A29</v>
+        <v/>
       </c>
       <c r="L117" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",L$1,"V",$D117,"A",$A117),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -21120,11 +19724,11 @@
       </c>
       <c r="B118" s="8" t="str">
         <f>IF(VLOOKUP($A118,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A118,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C118" s="8" t="str">
         <f>IF(VLOOKUP($A118,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A118,Assets!$A:$C,3,FALSE))</f>
-        <v>Data backup and disaster recovery procedures</v>
+        <v/>
       </c>
       <c r="D118" s="13">
         <v>4</v>
@@ -21185,18 +19789,18 @@
       </c>
       <c r="B119" t="str">
         <f>IF(VLOOKUP($A119,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A119,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C119" t="str">
         <f>IF(VLOOKUP($A119,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A119,Assets!$A:$C,3,FALSE))</f>
-        <v>Onboarding and offboarding procedures for staff</v>
+        <v/>
       </c>
       <c r="D119" s="12">
         <v>1</v>
       </c>
       <c r="E119" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D119,"A",$A119),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V1A30</v>
+        <v/>
       </c>
       <c r="F119" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D119,"A",$A119),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -21250,18 +19854,18 @@
       </c>
       <c r="B120" t="str">
         <f>IF(VLOOKUP($A120,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A120,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C120" t="str">
         <f>IF(VLOOKUP($A120,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A120,Assets!$A:$C,3,FALSE))</f>
-        <v>Onboarding and offboarding procedures for staff</v>
+        <v/>
       </c>
       <c r="D120" s="12">
         <v>2</v>
       </c>
       <c r="E120" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D120,"A",$A120),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V2A30</v>
+        <v/>
       </c>
       <c r="F120" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D120,"A",$A120),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -21315,11 +19919,11 @@
       </c>
       <c r="B121" t="str">
         <f>IF(VLOOKUP($A121,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A121,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C121" t="str">
         <f>IF(VLOOKUP($A121,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A121,Assets!$A:$C,3,FALSE))</f>
-        <v>Onboarding and offboarding procedures for staff</v>
+        <v/>
       </c>
       <c r="D121" s="12">
         <v>3</v>
@@ -21380,11 +19984,11 @@
       </c>
       <c r="B122" s="8" t="str">
         <f>IF(VLOOKUP($A122,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A122,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C122" s="8" t="str">
         <f>IF(VLOOKUP($A122,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A122,Assets!$A:$C,3,FALSE))</f>
-        <v>Onboarding and offboarding procedures for staff</v>
+        <v/>
       </c>
       <c r="D122" s="13">
         <v>4</v>
@@ -21445,18 +20049,18 @@
       </c>
       <c r="B123" t="str">
         <f>IF(VLOOKUP($A123,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A123,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C123" t="str">
         <f>IF(VLOOKUP($A123,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A123,Assets!$A:$C,3,FALSE))</f>
-        <v>Onboarding and offboarding procedures for customers</v>
+        <v/>
       </c>
       <c r="D123" s="12">
         <v>1</v>
       </c>
       <c r="E123" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D123,"A",$A123),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V1A31</v>
+        <v/>
       </c>
       <c r="F123" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D123,"A",$A123),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -21510,11 +20114,11 @@
       </c>
       <c r="B124" t="str">
         <f>IF(VLOOKUP($A124,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A124,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C124" t="str">
         <f>IF(VLOOKUP($A124,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A124,Assets!$A:$C,3,FALSE))</f>
-        <v>Onboarding and offboarding procedures for customers</v>
+        <v/>
       </c>
       <c r="D124" s="12">
         <v>2</v>
@@ -21533,7 +20137,7 @@
       </c>
       <c r="H124" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",H$1,"V",$D124,"A",$A124),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T4V2A31</v>
+        <v/>
       </c>
       <c r="I124" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D124,"A",$A124),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -21575,11 +20179,11 @@
       </c>
       <c r="B125" t="str">
         <f>IF(VLOOKUP($A125,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A125,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C125" t="str">
         <f>IF(VLOOKUP($A125,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A125,Assets!$A:$C,3,FALSE))</f>
-        <v>Onboarding and offboarding procedures for customers</v>
+        <v/>
       </c>
       <c r="D125" s="12">
         <v>3</v>
@@ -21640,11 +20244,11 @@
       </c>
       <c r="B126" s="8" t="str">
         <f>IF(VLOOKUP($A126,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A126,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C126" s="8" t="str">
         <f>IF(VLOOKUP($A126,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A126,Assets!$A:$C,3,FALSE))</f>
-        <v>Onboarding and offboarding procedures for customers</v>
+        <v/>
       </c>
       <c r="D126" s="13">
         <v>4</v>
@@ -21705,18 +20309,18 @@
       </c>
       <c r="B127" t="str">
         <f>IF(VLOOKUP($A127,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A127,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C127" t="str">
         <f>IF(VLOOKUP($A127,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A127,Assets!$A:$C,3,FALSE))</f>
-        <v>Risk management and business continuity planning</v>
+        <v/>
       </c>
       <c r="D127" s="12">
         <v>1</v>
       </c>
       <c r="E127" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D127,"A",$A127),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V1A32</v>
+        <v/>
       </c>
       <c r="F127" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D127,"A",$A127),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -21770,11 +20374,11 @@
       </c>
       <c r="B128" t="str">
         <f>IF(VLOOKUP($A128,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A128,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C128" t="str">
         <f>IF(VLOOKUP($A128,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A128,Assets!$A:$C,3,FALSE))</f>
-        <v>Risk management and business continuity planning</v>
+        <v/>
       </c>
       <c r="D128" s="12">
         <v>2</v>
@@ -21805,7 +20409,7 @@
       </c>
       <c r="K128" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",K$1,"V",$D128,"A",$A128),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T7V2A32</v>
+        <v/>
       </c>
       <c r="L128" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",L$1,"V",$D128,"A",$A128),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -21835,11 +20439,11 @@
       </c>
       <c r="B129" t="str">
         <f>IF(VLOOKUP($A129,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A129,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C129" t="str">
         <f>IF(VLOOKUP($A129,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A129,Assets!$A:$C,3,FALSE))</f>
-        <v>Risk management and business continuity planning</v>
+        <v/>
       </c>
       <c r="D129" s="12">
         <v>3</v>
@@ -21900,11 +20504,11 @@
       </c>
       <c r="B130" s="8" t="str">
         <f>IF(VLOOKUP($A130,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A130,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C130" s="8" t="str">
         <f>IF(VLOOKUP($A130,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A130,Assets!$A:$C,3,FALSE))</f>
-        <v>Risk management and business continuity planning</v>
+        <v/>
       </c>
       <c r="D130" s="13">
         <v>4</v>
@@ -21965,18 +20569,18 @@
       </c>
       <c r="B131" t="str">
         <f>IF(VLOOKUP($A131,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A131,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C131" t="str">
         <f>IF(VLOOKUP($A131,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A131,Assets!$A:$C,3,FALSE))</f>
-        <v>Physical security procedures (building and access control)</v>
+        <v/>
       </c>
       <c r="D131" s="12">
         <v>1</v>
       </c>
       <c r="E131" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D131,"A",$A131),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V1A33</v>
+        <v/>
       </c>
       <c r="F131" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D131,"A",$A131),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -22030,11 +20634,11 @@
       </c>
       <c r="B132" t="str">
         <f>IF(VLOOKUP($A132,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A132,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C132" t="str">
         <f>IF(VLOOKUP($A132,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A132,Assets!$A:$C,3,FALSE))</f>
-        <v>Physical security procedures (building and access control)</v>
+        <v/>
       </c>
       <c r="D132" s="12">
         <v>2</v>
@@ -22053,7 +20657,7 @@
       </c>
       <c r="H132" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",H$1,"V",$D132,"A",$A132),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T4V2A33</v>
+        <v/>
       </c>
       <c r="I132" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D132,"A",$A132),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -22095,11 +20699,11 @@
       </c>
       <c r="B133" t="str">
         <f>IF(VLOOKUP($A133,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A133,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C133" t="str">
         <f>IF(VLOOKUP($A133,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A133,Assets!$A:$C,3,FALSE))</f>
-        <v>Physical security procedures (building and access control)</v>
+        <v/>
       </c>
       <c r="D133" s="12">
         <v>3</v>
@@ -22160,11 +20764,11 @@
       </c>
       <c r="B134" s="8" t="str">
         <f>IF(VLOOKUP($A134,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A134,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C134" s="8" t="str">
         <f>IF(VLOOKUP($A134,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A134,Assets!$A:$C,3,FALSE))</f>
-        <v>Physical security procedures (building and access control)</v>
+        <v/>
       </c>
       <c r="D134" s="13">
         <v>4</v>
@@ -22225,18 +20829,18 @@
       </c>
       <c r="B135" t="str">
         <f>IF(VLOOKUP($A135,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A135,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C135" t="str">
         <f>IF(VLOOKUP($A135,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A135,Assets!$A:$C,3,FALSE))</f>
-        <v>IT service management and support workflows</v>
+        <v/>
       </c>
       <c r="D135" s="12">
         <v>1</v>
       </c>
       <c r="E135" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",E$1,"V",$D135,"A",$A135),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T1V1A34</v>
+        <v/>
       </c>
       <c r="F135" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",F$1,"V",$D135,"A",$A135),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -22290,11 +20894,11 @@
       </c>
       <c r="B136" t="str">
         <f>IF(VLOOKUP($A136,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A136,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C136" t="str">
         <f>IF(VLOOKUP($A136,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A136,Assets!$A:$C,3,FALSE))</f>
-        <v>IT service management and support workflows</v>
+        <v/>
       </c>
       <c r="D136" s="12">
         <v>2</v>
@@ -22313,7 +20917,7 @@
       </c>
       <c r="H136" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",H$1,"V",$D136,"A",$A136),Vulnerabilities!$G:$G,1,FALSE),"")</f>
-        <v>T4V2A34</v>
+        <v/>
       </c>
       <c r="I136" s="16" t="str">
         <f>_xlfn.IFNA(VLOOKUP(_xlfn.CONCAT("T",I$1,"V",$D136,"A",$A136),Vulnerabilities!$G:$G,1,FALSE),"")</f>
@@ -22355,11 +20959,11 @@
       </c>
       <c r="B137" t="str">
         <f>IF(VLOOKUP($A137,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A137,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C137" t="str">
         <f>IF(VLOOKUP($A137,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A137,Assets!$A:$C,3,FALSE))</f>
-        <v>IT service management and support workflows</v>
+        <v/>
       </c>
       <c r="D137" s="12">
         <v>3</v>
@@ -22420,11 +21024,11 @@
       </c>
       <c r="B138" s="8" t="str">
         <f>IF(VLOOKUP($A138,Assets!$A:$C,2,FALSE)=0,"",VLOOKUP($A138,Assets!$A:$C,2,FALSE))</f>
-        <v>Processes</v>
+        <v/>
       </c>
       <c r="C138" s="8" t="str">
         <f>IF(VLOOKUP($A138,Assets!$A:$C,3,FALSE)=0,"",VLOOKUP($A138,Assets!$A:$C,3,FALSE))</f>
-        <v>IT service management and support workflows</v>
+        <v/>
       </c>
       <c r="D138" s="13">
         <v>4</v>
@@ -39701,391 +38305,391 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C2" s="1" t="str">
         <f>_xlfn.CONCAT(A2,"|",B2)</f>
         <v>Very High|Very Low</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="C3" s="1" t="str">
         <f t="shared" ref="C3:C26" si="0">_xlfn.CONCAT(A3,"|",B3)</f>
         <v>High|Very Low</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C4" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Moderate|Very Low</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C5" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Low|Very Low</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C6" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Very Low|Very Low</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="C7" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Very High|Low</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C8" s="1" t="str">
         <f t="shared" si="0"/>
         <v>High|Low</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C9" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Moderate|Low</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Low|Low</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C11" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Very Low|Low</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C12" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Very High|Moderate</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C13" s="1" t="str">
         <f t="shared" si="0"/>
         <v>High|Moderate</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C14" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Moderate|Moderate</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C15" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Low|Moderate</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Very Low|Moderate</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Very High|High</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="str">
         <f t="shared" si="0"/>
         <v>High|High</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C19" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Moderate|High</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C20" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Low|High</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C21" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Very Low|High</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C22" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Very High|Very High</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C23" s="1" t="str">
         <f t="shared" si="0"/>
         <v>High|Very High</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C24" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Moderate|Very High</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C25" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Low|Very High</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C26" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Very Low|Very High</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
